--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="item_use" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2219,4 +2220,457 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>usable</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cost_on_use</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>use_cd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>use_time</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>use_type</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EItemUseType</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>usable</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>cost_on_use</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>use_cd</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>use_time</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>use_type</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>p1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>banana</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>j_drop_small</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>GiveDrop</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>evil_scroll_01</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UseAbility</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>queen_pull_all</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -129,24 +129,36 @@
     <t>##</t>
   </si>
   <si>
+    <t>jingyuan</t>
+  </si>
+  <si>
+    <t>精元</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>small_stone</t>
+  </si>
+  <si>
     <t>Normal</t>
   </si>
   <si>
     <t>Size1</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>small_stone</t>
-  </si>
-  <si>
     <t>stick</t>
   </si>
   <si>
@@ -184,9 +196,6 @@
   </si>
   <si>
     <t>gold</t>
-  </si>
-  <si>
-    <t>Currency</t>
   </si>
   <si>
     <t>NoLimit</t>
@@ -292,14 +301,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,148 +757,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1248,12 +1250,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="10.75" customWidth="1"/>
     <col min="3" max="3" width="12.125" customWidth="1"/>
     <col min="4" max="4" width="24.375" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="21.625" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -1521,13 +1527,13 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1542,7 +1548,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K5" t="b">
         <v>1</v>
@@ -1551,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -1566,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1575,122 +1581,60 @@
         <v>0</v>
       </c>
       <c r="U5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="B6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
-      <c r="U6" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
         <v>39</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7" t="s">
-        <v>37</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1704,16 +1648,16 @@
     </row>
     <row r="8" spans="1:21">
       <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="C8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1728,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K8" t="b">
         <v>1</v>
@@ -1737,7 +1681,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -1752,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1766,16 +1710,16 @@
     </row>
     <row r="9" spans="1:21">
       <c r="B9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -1790,7 +1734,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K9" t="b">
         <v>1</v>
@@ -1799,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N9">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1814,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1828,16 +1772,16 @@
     </row>
     <row r="10" spans="1:21">
       <c r="B10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1852,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K10" t="b">
         <v>1</v>
@@ -1861,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N10">
         <v>5000</v>
@@ -1876,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1890,16 +1834,16 @@
     </row>
     <row r="11" spans="1:21">
       <c r="B11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1914,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K11" t="b">
         <v>1</v>
@@ -1923,10 +1867,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -1938,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1952,16 +1896,16 @@
     </row>
     <row r="12" spans="1:21">
       <c r="B12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1976,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K12" t="b">
         <v>1</v>
@@ -1985,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2000,7 +1944,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -2014,16 +1958,16 @@
     </row>
     <row r="13" spans="1:21">
       <c r="B13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2038,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K13" t="b">
         <v>1</v>
@@ -2047,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2062,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2076,16 +2020,16 @@
     </row>
     <row r="14" spans="1:21">
       <c r="B14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2100,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
@@ -2109,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2124,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2138,16 +2082,16 @@
     </row>
     <row r="15" spans="1:21">
       <c r="B15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2162,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -2171,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2186,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2200,16 +2144,16 @@
     </row>
     <row r="16" spans="1:21">
       <c r="B16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2224,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>
@@ -2233,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2248,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2262,16 +2206,16 @@
     </row>
     <row r="17" spans="2:21">
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2286,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
@@ -2295,7 +2239,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2310,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -2324,32 +2268,32 @@
     </row>
     <row r="18" spans="2:21">
       <c r="B18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
         <v>56</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
         <v>57</v>
       </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>55</v>
-      </c>
       <c r="K18" t="b">
         <v>1</v>
       </c>
@@ -2357,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -2372,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2392,10 +2336,10 @@
         <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -2410,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -2419,7 +2363,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2434,7 +2378,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2448,17 +2392,17 @@
     </row>
     <row r="20" spans="2:21">
       <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" t="s">
         <v>60</v>
       </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" t="s">
-        <v>57</v>
-      </c>
       <c r="F20">
         <v>0</v>
       </c>
@@ -2472,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -2481,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -2496,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S20">
         <v>0</v>
@@ -2510,16 +2454,16 @@
     </row>
     <row r="21" spans="2:21">
       <c r="B21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2534,16 +2478,16 @@
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -2552,16 +2496,16 @@
         <v>0</v>
       </c>
       <c r="P21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="S21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T21" t="b">
         <v>0</v>
@@ -2578,10 +2522,10 @@
         <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2599,13 +2543,13 @@
         <v>65</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -2614,36 +2558,36 @@
         <v>0</v>
       </c>
       <c r="P22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R22" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:21">
       <c r="B23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -2658,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -2667,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -2682,15 +2626,77 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="T23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21">
+      <c r="B24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>69</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="s">
+        <v>38</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>39</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2711,46 +2717,46 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2779,7 +2785,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -2852,46 +2858,46 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2899,7 +2905,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2917,7 +2923,7 @@
         <v>1.5</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2937,7 +2943,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2955,7 +2961,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -2975,7 +2981,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2993,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3008,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="94">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,12 @@
     <t>##</t>
   </si>
   <si>
+    <t>自动销毁时间</t>
+  </si>
+  <si>
+    <t>特殊buffid</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -211,6 +217,48 @@
   </si>
   <si>
     <t>evil_scroll_01</t>
+  </si>
+  <si>
+    <t>desire_shard</t>
+  </si>
+  <si>
+    <t>欲望碎片</t>
+  </si>
+  <si>
+    <t>knowledge_shard</t>
+  </si>
+  <si>
+    <t>通识碎片</t>
+  </si>
+  <si>
+    <t>random_desire_crystal</t>
+  </si>
+  <si>
+    <t>随机欲望结晶</t>
+  </si>
+  <si>
+    <t>desire_crystal_01</t>
+  </si>
+  <si>
+    <t>欲望结晶-1</t>
+  </si>
+  <si>
+    <t>desire_crystal_02</t>
+  </si>
+  <si>
+    <t>欲望结晶-2</t>
+  </si>
+  <si>
+    <t>desire_crystal_03</t>
+  </si>
+  <si>
+    <t>欲望结晶-3</t>
+  </si>
+  <si>
+    <t>desire_crystal_04</t>
+  </si>
+  <si>
+    <t>欲望结晶-4</t>
   </si>
   <si>
     <t>id</t>
@@ -274,14 +322,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -737,148 +778,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1230,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="6" width="14.375" customWidth="1"/>
@@ -1458,10 +1499,10 @@
         <v>13</v>
       </c>
       <c r="O4" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="P4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="Q4" t="s">
         <v>16</v>
@@ -1475,13 +1516,13 @@
     </row>
     <row r="5" spans="1:19">
       <c r="B5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1490,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1499,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1525,13 +1566,13 @@
     </row>
     <row r="6" spans="1:19">
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1540,7 +1581,7 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -1549,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1575,13 +1616,13 @@
     </row>
     <row r="7" spans="1:19">
       <c r="B7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -1590,19 +1631,19 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
         <v>35</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>33</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1628,13 +1669,13 @@
     </row>
     <row r="8" spans="1:19">
       <c r="B8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -1643,10 +1684,10 @@
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -1655,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1681,13 +1722,13 @@
     </row>
     <row r="9" spans="1:19">
       <c r="B9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1696,7 +1737,7 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -1705,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L9">
         <v>5000</v>
@@ -1731,13 +1772,13 @@
     </row>
     <row r="10" spans="1:19">
       <c r="B10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -1746,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -1755,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L10">
         <v>5000</v>
@@ -1781,13 +1822,13 @@
     </row>
     <row r="11" spans="1:19">
       <c r="B11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -1796,7 +1837,7 @@
         <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -1805,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1831,13 +1872,13 @@
     </row>
     <row r="12" spans="1:19">
       <c r="B12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1846,7 +1887,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -1855,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1881,13 +1922,13 @@
     </row>
     <row r="13" spans="1:19">
       <c r="B13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -1896,7 +1937,7 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1905,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1931,13 +1972,13 @@
     </row>
     <row r="14" spans="1:19">
       <c r="B14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -1946,7 +1987,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -1955,7 +1996,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1981,13 +2022,13 @@
     </row>
     <row r="15" spans="1:19">
       <c r="B15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -1996,7 +2037,7 @@
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -2005,7 +2046,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2031,13 +2072,13 @@
     </row>
     <row r="16" spans="1:19">
       <c r="B16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -2046,7 +2087,7 @@
         <v>999999</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -2055,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2081,13 +2122,13 @@
     </row>
     <row r="17" spans="2:19">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -2096,7 +2137,7 @@
         <v>999999</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -2105,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2131,13 +2172,13 @@
     </row>
     <row r="18" spans="2:19">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -2146,7 +2187,7 @@
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -2155,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2181,13 +2222,13 @@
     </row>
     <row r="19" spans="2:19">
       <c r="B19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -2196,7 +2237,7 @@
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -2205,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2231,13 +2272,13 @@
     </row>
     <row r="20" spans="2:19">
       <c r="B20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -2246,7 +2287,7 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -2255,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2281,13 +2322,13 @@
     </row>
     <row r="21" spans="2:19">
       <c r="B21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -2296,7 +2337,7 @@
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -2305,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2320,7 +2361,7 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -2334,13 +2375,13 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -2349,7 +2390,7 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
@@ -2358,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -2384,13 +2425,13 @@
     </row>
     <row r="23" spans="2:19">
       <c r="B23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -2399,7 +2440,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -2408,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2429,6 +2470,329 @@
         <v>0</v>
       </c>
       <c r="S23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19">
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25">
+        <v>999999</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
+      <c r="B26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>999999</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>35</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19">
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" t="s">
+        <v>34</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19">
+      <c r="B30" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>71</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19">
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
+        <v>35</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:19">
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>35</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2441,54 +2805,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="J1" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="K1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="M1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="N1" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2517,7 +2881,7 @@
         <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="J2" t="s">
         <v>26</v>
@@ -2590,46 +2954,46 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="J4" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="K4" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="L4" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="M4" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O4" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2637,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2655,7 +3019,7 @@
         <v>1.5</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2675,7 +3039,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2693,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -2713,7 +3077,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2731,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2746,7 +3110,33 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>77</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="96">
   <si>
     <t>##var</t>
   </si>
@@ -306,10 +306,16 @@
     <t>GiveDrop</t>
   </si>
   <si>
-    <t>UseAbility</t>
+    <t>UseSkill</t>
   </si>
   <si>
     <t>queen_pull_all</t>
+  </si>
+  <si>
+    <t>feidao</t>
+  </si>
+  <si>
+    <t>shoot_feidao</t>
   </si>
 </sst>
 </file>
@@ -2805,7 +2811,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -3004,7 +3010,7 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -3042,7 +3048,7 @@
         <v>61</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -3080,7 +3086,7 @@
         <v>62</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -3120,6 +3126,9 @@
       <c r="C9" t="s">
         <v>67</v>
       </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
@@ -3137,6 +3146,47 @@
       </c>
       <c r="J9">
         <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -259,6 +259,12 @@
   </si>
   <si>
     <t>欲望结晶-4</t>
+  </si>
+  <si>
+    <t>rumor_points</t>
+  </si>
+  <si>
+    <t>流言点</t>
   </si>
   <si>
     <t>id</t>
@@ -1277,7 +1283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="6" width="14.375" customWidth="1"/>
@@ -2799,6 +2805,56 @@
         <v>0</v>
       </c>
       <c r="S32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19">
+      <c r="B34" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>77</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>35</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2819,46 +2875,46 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2887,7 +2943,7 @@
         <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J2" t="s">
         <v>26</v>
@@ -2960,46 +3016,46 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3063,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3101,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3116,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -3142,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -3153,7 +3209,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3171,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3186,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -2816,13 +2816,13 @@
         <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>999999</v>
       </c>
       <c r="H34" t="s">
         <v>77</v>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -219,6 +219,12 @@
     <t>evil_scroll_01</t>
   </si>
   <si>
+    <t>small_knife</t>
+  </si>
+  <si>
+    <t>飞刀</t>
+  </si>
+  <si>
     <t>desire_shard</t>
   </si>
   <si>
@@ -318,10 +324,7 @@
     <t>queen_pull_all</t>
   </si>
   <si>
-    <t>feidao</t>
-  </si>
-  <si>
-    <t>shoot_feidao</t>
+    <t>shoot_knife</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1286,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="6" width="14.375" customWidth="1"/>
@@ -2493,16 +2496,19 @@
         <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>999999</v>
+        <v>99</v>
+      </c>
+      <c r="H25" t="s">
+        <v>63</v>
       </c>
       <c r="I25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -2532,80 +2538,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:19">
-      <c r="B26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>999999</v>
-      </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s">
-        <v>35</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26" t="b">
-        <v>0</v>
-      </c>
-      <c r="S26" t="b">
-        <v>0</v>
-      </c>
-    </row>
     <row r="27" spans="2:19">
       <c r="B27" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>999999</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>35</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="B28" t="s">
         <v>67</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>68</v>
       </c>
-      <c r="D27" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>67</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27" t="b">
-        <v>1</v>
+      <c r="D28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>999999</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" t="s">
+        <v>35</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:19">
@@ -2630,90 +2654,19 @@
       <c r="I29" t="b">
         <v>0</v>
       </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>35</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
       <c r="S29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:19">
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>34</v>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>71</v>
-      </c>
-      <c r="I30" t="b">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" t="s">
-        <v>35</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
-      <c r="S30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D31" t="s">
         <v>34</v>
@@ -2725,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -2760,10 +2713,10 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
@@ -2775,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -2805,6 +2758,56 @@
         <v>0</v>
       </c>
       <c r="S32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19">
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>35</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2816,13 +2819,13 @@
         <v>78</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>999999</v>
+        <v>1</v>
       </c>
       <c r="H34" t="s">
         <v>77</v>
@@ -2855,6 +2858,56 @@
         <v>0</v>
       </c>
       <c r="S34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19">
+      <c r="B36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>999999</v>
+      </c>
+      <c r="H36" t="s">
+        <v>79</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" t="s">
+        <v>35</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2875,46 +2928,46 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -2943,7 +2996,7 @@
         <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J2" t="s">
         <v>26</v>
@@ -3016,46 +3069,46 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3119,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3157,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3172,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -3180,7 +3233,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3198,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -3209,7 +3262,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3227,7 +3280,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3242,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -270,7 +270,7 @@
     <t>rumor_points</t>
   </si>
   <si>
-    <t>流言点</t>
+    <t>秘闻</t>
   </si>
   <si>
     <t>id</t>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,9 @@
     <t>is_auto_use</t>
   </si>
   <si>
+    <t>quick_bar_kind</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -114,6 +117,9 @@
     <t>float</t>
   </si>
   <si>
+    <t>EQuickBarItemKind</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -127,6 +133,9 @@
   </si>
   <si>
     <t>特殊buffid</t>
+  </si>
+  <si>
+    <t>快速使用类型</t>
   </si>
   <si>
     <t>1</t>
@@ -1286,14 +1295,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:T36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="6" width="14.375" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1351,128 +1360,137 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" t="s">
         <v>21</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>23</v>
+      </c>
+      <c r="T2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="S3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>31</v>
+      </c>
+      <c r="T3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -1514,10 +1532,10 @@
         <v>13</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="P4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q4" t="s">
         <v>16</v>
@@ -1528,16 +1546,19 @@
       <c r="S4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:19">
+      <c r="T4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="B5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1546,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -1555,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1579,15 +1600,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:20">
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1596,7 +1617,7 @@
         <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -1605,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1629,15 +1650,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:20">
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
         <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -1646,51 +1667,51 @@
         <v>5</v>
       </c>
       <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" t="s">
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
         <v>37</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7" t="b">
-        <v>0</v>
-      </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -1699,10 +1720,10 @@
         <v>5</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -1711,7 +1732,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1735,15 +1756,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:20">
       <c r="B9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1752,7 +1773,7 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -1761,7 +1782,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L9">
         <v>5000</v>
@@ -1785,15 +1806,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:20">
       <c r="B10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -1802,7 +1823,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -1811,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L10">
         <v>5000</v>
@@ -1835,15 +1856,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:20">
       <c r="B11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -1852,7 +1873,7 @@
         <v>5</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -1861,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -1885,15 +1906,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:20">
       <c r="B12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1902,7 +1923,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -1911,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1935,15 +1956,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:20">
       <c r="B13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -1952,7 +1973,7 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1961,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1985,15 +2006,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:20">
       <c r="B14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -2002,7 +2023,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -2011,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2035,15 +2056,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:20">
       <c r="B15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -2052,7 +2073,7 @@
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -2061,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2085,15 +2106,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:20">
       <c r="B16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -2102,7 +2123,7 @@
         <v>999999</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -2111,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2137,13 +2158,13 @@
     </row>
     <row r="17" spans="2:19">
       <c r="B17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -2152,7 +2173,7 @@
         <v>999999</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -2161,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2187,13 +2208,13 @@
     </row>
     <row r="18" spans="2:19">
       <c r="B18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
@@ -2202,7 +2223,7 @@
         <v>5</v>
       </c>
       <c r="H18" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -2211,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2237,13 +2258,13 @@
     </row>
     <row r="19" spans="2:19">
       <c r="B19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -2252,7 +2273,7 @@
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -2261,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2287,13 +2308,13 @@
     </row>
     <row r="20" spans="2:19">
       <c r="B20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -2302,7 +2323,7 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -2311,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2337,13 +2358,13 @@
     </row>
     <row r="21" spans="2:19">
       <c r="B21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -2352,7 +2373,7 @@
         <v>5</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I21" t="b">
         <v>0</v>
@@ -2361,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2376,7 +2397,7 @@
         <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="Q21">
         <v>5</v>
@@ -2390,13 +2411,13 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -2405,7 +2426,7 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
@@ -2414,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -2440,13 +2461,13 @@
     </row>
     <row r="23" spans="2:19">
       <c r="B23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -2455,7 +2476,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -2464,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2490,13 +2511,13 @@
     </row>
     <row r="25" spans="2:19">
       <c r="B25" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -2505,7 +2526,7 @@
         <v>99</v>
       </c>
       <c r="H25" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -2514,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -2540,13 +2561,13 @@
     </row>
     <row r="27" spans="2:19">
       <c r="B27" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D27" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -2561,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2587,13 +2608,13 @@
     </row>
     <row r="28" spans="2:19">
       <c r="B28" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -2608,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2634,13 +2655,13 @@
     </row>
     <row r="29" spans="2:19">
       <c r="B29" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -2649,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I29" t="b">
         <v>0</v>
@@ -2663,13 +2684,13 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -2678,7 +2699,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -2687,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -2713,13 +2734,13 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -2728,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -2737,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2763,13 +2784,13 @@
     </row>
     <row r="33" spans="2:19">
       <c r="B33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -2778,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -2787,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2813,13 +2834,13 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -2828,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -2837,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -2863,13 +2884,13 @@
     </row>
     <row r="36" spans="2:19">
       <c r="B36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -2878,7 +2899,7 @@
         <v>999999</v>
       </c>
       <c r="H36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -2887,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -2928,187 +2949,187 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
       <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="N4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="O4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3116,7 +3137,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3134,7 +3155,7 @@
         <v>1.5</v>
       </c>
       <c r="I5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3154,7 +3175,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3172,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3192,7 +3213,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3210,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3225,7 +3246,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -3233,7 +3254,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3251,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -3262,7 +3283,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3280,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3295,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="103">
   <si>
     <t>##var</t>
   </si>
@@ -138,18 +138,24 @@
     <t>快速使用类型</t>
   </si>
   <si>
-    <t>1</t>
+    <t>jingyuan</t>
+  </si>
+  <si>
+    <t>精元</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>small_stone</t>
   </si>
   <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>small_stone</t>
-  </si>
-  <si>
     <t>stick</t>
   </si>
   <si>
@@ -187,9 +193,6 @@
   </si>
   <si>
     <t>gold</t>
-  </si>
-  <si>
-    <t>Currency</t>
   </si>
   <si>
     <t>j</t>
@@ -1295,7 +1298,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="6" max="6" width="14.375" customWidth="1"/>
@@ -1555,16 +1558,19 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>500</v>
+      </c>
+      <c r="G5" t="s">
         <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
       </c>
       <c r="H5" t="s">
         <v>36</v>
@@ -1576,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1597,56 +1603,6 @@
         <v>0</v>
       </c>
       <c r="S5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="B6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-      <c r="S6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1658,7 +1614,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -1666,9 +1622,6 @@
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
       <c r="H7" t="s">
         <v>40</v>
       </c>
@@ -1679,7 +1632,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1711,7 +1664,7 @@
         <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -1732,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1764,7 +1717,7 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
@@ -1772,6 +1725,9 @@
       <c r="F9">
         <v>5</v>
       </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
       <c r="H9" t="s">
         <v>44</v>
       </c>
@@ -1782,10 +1738,10 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L9">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -1814,7 +1770,7 @@
         <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -1832,7 +1788,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L10">
         <v>5000</v>
@@ -1858,13 +1814,13 @@
     </row>
     <row r="11" spans="1:20">
       <c r="B11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -1873,19 +1829,19 @@
         <v>5</v>
       </c>
       <c r="H11" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
         <v>47</v>
       </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="s">
-        <v>38</v>
-      </c>
       <c r="L11">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -1908,13 +1864,13 @@
     </row>
     <row r="12" spans="1:20">
       <c r="B12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1923,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -1932,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1958,13 +1914,13 @@
     </row>
     <row r="13" spans="1:20">
       <c r="B13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -1973,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1982,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -2008,13 +1964,13 @@
     </row>
     <row r="14" spans="1:20">
       <c r="B14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -2023,7 +1979,7 @@
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -2032,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -2058,13 +2014,13 @@
     </row>
     <row r="15" spans="1:20">
       <c r="B15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -2073,7 +2029,7 @@
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -2082,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -2108,23 +2064,23 @@
     </row>
     <row r="16" spans="1:20">
       <c r="B16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
         <v>53</v>
       </c>
-      <c r="E16" t="b">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>999999</v>
-      </c>
-      <c r="H16" t="s">
-        <v>52</v>
-      </c>
       <c r="I16" t="b">
         <v>1</v>
       </c>
@@ -2132,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2164,7 +2120,7 @@
         <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -2182,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -2214,13 +2170,13 @@
         <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>999999</v>
       </c>
       <c r="H18" t="s">
         <v>55</v>
@@ -2232,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -2258,13 +2214,13 @@
     </row>
     <row r="19" spans="2:19">
       <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
         <v>57</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -2273,7 +2229,7 @@
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -2282,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2308,13 +2264,13 @@
     </row>
     <row r="20" spans="2:19">
       <c r="B20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -2323,7 +2279,7 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -2332,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2358,13 +2314,13 @@
     </row>
     <row r="21" spans="2:19">
       <c r="B21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -2376,13 +2332,13 @@
         <v>61</v>
       </c>
       <c r="I21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -2391,16 +2347,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>30</v>
-      </c>
-      <c r="P21" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="b">
         <v>0</v>
@@ -2411,13 +2364,13 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -2426,37 +2379,40 @@
         <v>5</v>
       </c>
       <c r="H22" t="s">
+        <v>62</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" t="s">
+        <v>39</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>30</v>
+      </c>
+      <c r="P22" t="s">
         <v>64</v>
       </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22" t="s">
-        <v>38</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
       <c r="Q22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:19">
@@ -2467,10 +2423,10 @@
         <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -2485,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -2503,118 +2459,121 @@
         <v>0</v>
       </c>
       <c r="R23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:19">
-      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
+      <c r="B24" t="s">
         <v>66</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24">
+        <v>5</v>
+      </c>
+      <c r="H24" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
+        <v>39</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
+      <c r="B26" t="s">
         <v>67</v>
       </c>
-      <c r="D25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25">
+      <c r="C26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26">
         <v>99</v>
       </c>
-      <c r="H25" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25" t="b">
-        <v>0</v>
-      </c>
-      <c r="S25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:19">
-      <c r="B27" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" t="s">
-        <v>53</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>999999</v>
-      </c>
-      <c r="I27" t="b">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27" t="s">
-        <v>38</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27" t="b">
-        <v>0</v>
-      </c>
-      <c r="S27" t="b">
+      <c r="H26" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" t="s">
+        <v>39</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:19">
       <c r="B28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" t="s">
         <v>70</v>
       </c>
-      <c r="C28" t="s">
-        <v>71</v>
-      </c>
       <c r="D28" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -2629,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2655,92 +2614,89 @@
     </row>
     <row r="29" spans="2:19">
       <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
         <v>72</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>999999</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" t="s">
+        <v>39</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:19">
+      <c r="B30" t="s">
         <v>73</v>
       </c>
-      <c r="D29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="H29" t="s">
-        <v>72</v>
-      </c>
-      <c r="I29" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29" t="b">
-        <v>0</v>
-      </c>
-      <c r="S29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:19">
-      <c r="B31" t="s">
+      <c r="C30" t="s">
         <v>74</v>
       </c>
-      <c r="C31" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" t="s">
-        <v>37</v>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>74</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>38</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31" t="b">
-        <v>0</v>
+      <c r="D30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" t="s">
         <v>76</v>
       </c>
-      <c r="C32" t="s">
-        <v>77</v>
-      </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
@@ -2749,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -2758,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -2784,13 +2740,13 @@
     </row>
     <row r="33" spans="2:19">
       <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
         <v>78</v>
       </c>
-      <c r="C33" t="s">
-        <v>79</v>
-      </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -2799,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -2808,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -2834,101 +2790,151 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" t="s">
         <v>80</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>39</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19">
+      <c r="B35" t="s">
         <v>81</v>
       </c>
-      <c r="D34" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="H34" t="s">
-        <v>80</v>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
+      <c r="C35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>81</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" t="s">
+        <v>39</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19">
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" t="s">
         <v>38</v>
       </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:19">
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="E37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>999999</v>
+      </c>
+      <c r="H37" t="s">
         <v>83</v>
       </c>
-      <c r="D36" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>999999</v>
-      </c>
-      <c r="H36" t="s">
-        <v>82</v>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36" t="s">
-        <v>38</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" t="b">
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" t="s">
+        <v>39</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2949,46 +2955,46 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -3017,7 +3023,7 @@
         <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J2" t="s">
         <v>27</v>
@@ -3090,46 +3096,46 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3137,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -3155,7 +3161,7 @@
         <v>1.5</v>
       </c>
       <c r="I5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3175,7 +3181,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -3193,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3213,7 +3219,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -3231,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3246,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -3254,7 +3260,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3272,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -3283,7 +3289,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3301,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3316,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -2369,6 +2369,11 @@
       <c r="S19" t="b">
         <v>0</v>
       </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -2675,6 +2680,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
@@ -2734,7 +2740,13 @@
       <c r="S26" t="b">
         <v>0</v>
       </c>
-    </row>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
@@ -2882,6 +2894,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
@@ -3122,6 +3135,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -260,6 +260,12 @@
   </si>
   <si>
     <t>飞刀</t>
+  </si>
+  <si>
+    <t>smoke_grenade</t>
+  </si>
+  <si>
+    <t>烟雾弹</t>
   </si>
   <si>
     <t>desire_shard</t>
@@ -1347,7 +1353,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -2784,16 +2790,19 @@
         <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>999999</v>
+        <v>8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>77</v>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2823,80 +2832,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:20">
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" t="s">
-        <v>38</v>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>999999</v>
-      </c>
-      <c r="I31" t="b">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" t="s">
-        <v>39</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
-      <c r="S31" t="b">
-        <v>0</v>
-      </c>
-    </row>
     <row r="32" spans="2:20">
       <c r="B32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32">
+        <v>999999</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" t="s">
+        <v>39</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19">
+      <c r="B33" t="s">
         <v>81</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>82</v>
       </c>
-      <c r="D32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="H32" t="s">
-        <v>81</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32" t="b">
-        <v>1</v>
+      <c r="D33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <v>999999</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" t="s">
+        <v>39</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:19">
@@ -2921,90 +2948,19 @@
       <c r="I34" t="b">
         <v>0</v>
       </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34" t="s">
-        <v>39</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
       <c r="S34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:19">
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="H35" t="s">
-        <v>85</v>
-      </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35" t="s">
-        <v>39</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35" t="b">
-        <v>0</v>
-      </c>
-      <c r="S35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="2:19">
       <c r="B36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
         <v>44</v>
@@ -3016,7 +2972,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I36" t="b">
         <v>0</v>
@@ -3051,10 +3007,10 @@
     </row>
     <row r="37" spans="2:19">
       <c r="B37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
         <v>44</v>
@@ -3066,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -3096,6 +3052,56 @@
         <v>0</v>
       </c>
       <c r="S37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19">
+      <c r="B38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C38" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>89</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" t="s">
+        <v>39</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3107,13 +3113,13 @@
         <v>92</v>
       </c>
       <c r="D39" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>999999</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
         <v>91</v>
@@ -3149,43 +3155,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:19">
-      <c r="B40" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" t="s">
-        <v>94</v>
-      </c>
-      <c r="D40" t="s">
-        <v>38</v>
-      </c>
-      <c r="E40" t="b">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>999999</v>
-      </c>
-      <c r="I40" t="b">
-        <v>1</v>
-      </c>
-    </row>
     <row r="41" spans="2:19">
       <c r="B41" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
         <v>38</v>
       </c>
       <c r="E41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41">
         <v>999999</v>
       </c>
+      <c r="H41" t="s">
+        <v>93</v>
+      </c>
       <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41" t="s">
+        <v>39</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="b">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19">
+      <c r="B42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>999999</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19">
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>999999</v>
+      </c>
+      <c r="I43" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3198,54 +3254,57 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="21.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -3274,7 +3333,7 @@
         <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J2" t="s">
         <v>27</v>
@@ -3347,46 +3406,46 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3450,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3488,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3503,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -3511,7 +3570,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3529,7 +3588,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -3558,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3573,7 +3632,48 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
         <v>114</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3596,10 +3696,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3610,7 +3710,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -3638,10 +3738,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3649,7 +3749,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D5">
         <v>2</v>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="125">
   <si>
     <t>##var</t>
   </si>
@@ -268,6 +268,15 @@
     <t>烟雾弹</t>
   </si>
   <si>
+    <t>Consumable</t>
+  </si>
+  <si>
+    <t>sound_ball</t>
+  </si>
+  <si>
+    <t>声玉</t>
+  </si>
+  <si>
     <t>desire_shard</t>
   </si>
   <si>
@@ -380,6 +389,9 @@
   </si>
   <si>
     <t>shoot_knife</t>
+  </si>
+  <si>
+    <t>item_throw_smoke_grenade</t>
   </si>
   <si>
     <t>gift_tags</t>
@@ -1353,7 +1365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T43"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -2831,60 +2843,69 @@
       <c r="S30" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:20">
-      <c r="B32" t="s">
+      <c r="T30" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="31" spans="2:20">
+      <c r="B31" t="s">
         <v>80</v>
       </c>
-      <c r="D32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <v>999999</v>
-      </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32" t="s">
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="H31" t="s">
+        <v>80</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" t="s">
         <v>39</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>0</v>
-      </c>
-      <c r="S32" t="b">
-        <v>0</v>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="2:19">
       <c r="B33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
@@ -2928,89 +2949,86 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>999999</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" t="s">
+        <v>39</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19">
+      <c r="B35" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" t="s">
         <v>44</v>
       </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="H34" t="s">
-        <v>83</v>
-      </c>
-      <c r="I34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
-      </c>
-      <c r="S34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:19">
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="E35" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
         <v>86</v>
       </c>
-      <c r="D36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="s">
-        <v>85</v>
-      </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
-      <c r="K36" t="s">
-        <v>39</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36" t="b">
-        <v>0</v>
-      </c>
-      <c r="S36" t="b">
-        <v>0</v>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:19">
       <c r="B37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
         <v>44</v>
@@ -3022,7 +3040,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -3057,10 +3075,10 @@
     </row>
     <row r="38" spans="2:19">
       <c r="B38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
         <v>44</v>
@@ -3072,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -3107,10 +3125,10 @@
     </row>
     <row r="39" spans="2:19">
       <c r="B39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D39" t="s">
         <v>44</v>
@@ -3122,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -3155,82 +3173,112 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:19">
-      <c r="B41" t="s">
-        <v>93</v>
-      </c>
-      <c r="C41" t="s">
+    <row r="40" spans="2:19">
+      <c r="B40" t="s">
         <v>94</v>
       </c>
-      <c r="D41" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>999999</v>
-      </c>
-      <c r="H41" t="s">
-        <v>93</v>
-      </c>
-      <c r="I41" t="b">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41" t="s">
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="s">
+        <v>94</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" t="s">
         <v>39</v>
       </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="R41" t="b">
-        <v>0</v>
-      </c>
-      <c r="S41" t="b">
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="b">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:19">
       <c r="B42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D42" t="s">
         <v>38</v>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <v>999999</v>
       </c>
+      <c r="H42" t="s">
+        <v>96</v>
+      </c>
       <c r="I42" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>39</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="b">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42" t="b">
+        <v>0</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:19">
       <c r="B43" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D43" t="s">
         <v>38</v>
@@ -3242,6 +3290,26 @@
         <v>999999</v>
       </c>
       <c r="I43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19">
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>999999</v>
+      </c>
+      <c r="I44" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3254,7 +3322,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="21.75" customWidth="1"/>
@@ -3265,46 +3333,46 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -3333,7 +3401,7 @@
         <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J2" t="s">
         <v>27</v>
@@ -3406,46 +3474,46 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="I4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="L4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="N4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="O4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3509,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3547,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3562,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -3570,7 +3638,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -3588,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -3617,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3632,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -3658,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3673,7 +3741,48 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>116</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="B12">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3696,10 +3805,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3710,7 +3819,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -3738,10 +3847,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3749,7 +3858,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D5">
         <v>2</v>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="149">
   <si>
     <t>##var</t>
   </si>
@@ -368,6 +368,45 @@
   </si>
   <si>
     <t>尾铃</t>
+  </si>
+  <si>
+    <t>mind_facet_01</t>
+  </si>
+  <si>
+    <t>酣眠</t>
+  </si>
+  <si>
+    <t>MindFacet</t>
+  </si>
+  <si>
+    <t>mind_facet_02</t>
+  </si>
+  <si>
+    <t>一晌贪欢</t>
+  </si>
+  <si>
+    <t>mind_facet_03</t>
+  </si>
+  <si>
+    <t>灯影</t>
+  </si>
+  <si>
+    <t>mind_facet_04</t>
+  </si>
+  <si>
+    <t>幽闭之间</t>
+  </si>
+  <si>
+    <t>mind_facet_05</t>
+  </si>
+  <si>
+    <t>燃烧</t>
+  </si>
+  <si>
+    <t>mind_facet_06</t>
+  </si>
+  <si>
+    <t>夜色</t>
   </si>
   <si>
     <t>id</t>
@@ -1398,7 +1437,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -3531,6 +3570,306 @@
         <v>0</v>
       </c>
       <c r="S49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:19">
+      <c r="B51" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" t="s">
+        <v>115</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>9999</v>
+      </c>
+      <c r="H51" t="s">
+        <v>113</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" t="s">
+        <v>39</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>0</v>
+      </c>
+      <c r="R51" t="b">
+        <v>0</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:19">
+      <c r="B52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>9999</v>
+      </c>
+      <c r="H52" t="s">
+        <v>113</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52" t="s">
+        <v>39</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52" t="b">
+        <v>0</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:19">
+      <c r="B53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C53" t="s">
+        <v>119</v>
+      </c>
+      <c r="D53" t="s">
+        <v>115</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>9999</v>
+      </c>
+      <c r="H53" t="s">
+        <v>113</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53" t="s">
+        <v>39</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53" t="b">
+        <v>0</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:19">
+      <c r="B54" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" t="s">
+        <v>115</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>9999</v>
+      </c>
+      <c r="H54" t="s">
+        <v>113</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" t="s">
+        <v>39</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54" t="b">
+        <v>0</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19">
+      <c r="B55" t="s">
+        <v>122</v>
+      </c>
+      <c r="C55" t="s">
+        <v>123</v>
+      </c>
+      <c r="D55" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55">
+        <v>9999</v>
+      </c>
+      <c r="H55" t="s">
+        <v>113</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55" t="s">
+        <v>39</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55" t="b">
+        <v>0</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19">
+      <c r="B56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" t="s">
+        <v>115</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56">
+        <v>9999</v>
+      </c>
+      <c r="H56" t="s">
+        <v>113</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56" t="s">
+        <v>39</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56" t="b">
+        <v>0</v>
+      </c>
+      <c r="S56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -3554,46 +3893,46 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H1" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I1" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="J1" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="K1" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M1" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="N1" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="O1" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -3622,7 +3961,7 @@
         <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J2" t="s">
         <v>27</v>
@@ -3695,46 +4034,46 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="F4" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H4" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="I4" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="J4" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="K4" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="L4" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="M4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="N4" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="O4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -3798,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -3836,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3851,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -3877,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -3906,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3921,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -3947,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3962,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -3988,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4003,7 +4342,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -4026,10 +4365,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D1" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4040,7 +4379,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -4068,10 +4407,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4079,7 +4418,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="D5">
         <v>2</v>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="155">
   <si>
     <t>##var</t>
   </si>
@@ -409,6 +409,15 @@
     <t>夜色</t>
   </si>
   <si>
+    <t>rune_unlock_lady_up_1</t>
+  </si>
+  <si>
+    <t>rune_unlock</t>
+  </si>
+  <si>
+    <t>rune_unlock_lady_up_2</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -464,6 +473,15 @@
   </si>
   <si>
     <t>item_throw_smoke_grenade</t>
+  </si>
+  <si>
+    <t>UnlockRuneUpgrade</t>
+  </si>
+  <si>
+    <t>lady_up_1</t>
+  </si>
+  <si>
+    <t>lady_up_2</t>
   </si>
   <si>
     <t>gift_tags</t>
@@ -1437,7 +1455,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.375" customWidth="1"/>
@@ -1445,6 +1463,9 @@
     <col min="6" max="6" width="14.375" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="14" max="14" width="17.75" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="19" max="19" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
@@ -3871,6 +3892,94 @@
       </c>
       <c r="S56" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:19">
+      <c r="B58" t="s">
+        <v>126</v>
+      </c>
+      <c r="D58" t="s">
+        <v>44</v>
+      </c>
+      <c r="E58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
+        <v>127</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58" t="s">
+        <v>39</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58" t="b">
+        <v>0</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:19">
+      <c r="B59" t="s">
+        <v>128</v>
+      </c>
+      <c r="D59" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
+        <v>127</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59" t="s">
+        <v>39</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59" t="b">
+        <v>0</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3882,7 +3991,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="21.75" customWidth="1"/>
@@ -3893,46 +4002,46 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -3961,7 +4070,7 @@
         <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J2" t="s">
         <v>27</v>
@@ -4034,46 +4143,46 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="L4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="N4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="O4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -4137,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -4175,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -4190,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -4216,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J9">
         <v>99</v>
@@ -4245,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4260,7 +4369,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -4286,7 +4395,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4301,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -4327,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4342,7 +4451,89 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14" t="s">
+        <v>148</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>148</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4365,10 +4556,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -4379,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -4407,10 +4598,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4418,7 +4609,7 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D5">
         <v>2</v>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.375" customWidth="1" min="2" max="2"/>
@@ -4334,6 +4334,906 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>item_jingyuan_codex_orc</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>兽人精元样本</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>99</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>item_jingyuan_codex_orc</t>
+        </is>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="b">
+        <v>0</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>j_drop_orc_common</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>兽人精元滴</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>99</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>j_drop_orc_common</t>
+        </is>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="b">
+        <v>1</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>j_drop_orc_elite</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>兽人精英精元滴</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>99</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>j_drop_orc_elite</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="b">
+        <v>1</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>j_drop_sign_aries</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sign_aries滴</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E67" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>j_drop_sign_aries</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="b">
+        <v>1</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>j_drop_sign_taurus</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sign_taurus滴</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E68" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>j_drop_sign_taurus</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="b">
+        <v>1</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>j_drop_sign_gemini</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sign_gemini滴</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E69" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>j_drop_sign_gemini</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="b">
+        <v>1</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>j_drop_sign_cancer</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sign_cancer滴</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E70" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>j_drop_sign_cancer</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="b">
+        <v>1</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>j_drop_sign_leo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sign_leo滴</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E71" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>j_drop_sign_leo</t>
+        </is>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="b">
+        <v>1</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>j_drop_sign_virgo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sign_virgo滴</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E72" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>j_drop_sign_virgo</t>
+        </is>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="b">
+        <v>1</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>j_drop_sign_libra</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sign_libra滴</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E73" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>j_drop_sign_libra</t>
+        </is>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="b">
+        <v>1</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>j_drop_sign_scorpio</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sign_scorpio滴</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E74" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>j_drop_sign_scorpio</t>
+        </is>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="b">
+        <v>1</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>j_drop_sign_sagittarius</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sign_sagittarius滴</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E75" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>j_drop_sign_sagittarius</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="b">
+        <v>1</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>j_drop_sign_capricorn</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sign_capricorn滴</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E76" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>j_drop_sign_capricorn</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="b">
+        <v>1</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>j_drop_sign_aquarius</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sign_aquarius滴</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E77" t="b">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>j_drop_sign_aquarius</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="b">
+        <v>1</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>j_drop_sign_pisces</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sign_pisces滴</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E78" t="b">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>j_drop_sign_pisces</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="b">
+        <v>1</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4345,10 +5245,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="21.75" customWidth="1" min="3" max="3"/>
+    <col width="24.875" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4727,7 +5628,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GiveDrop</t>
+          <t>AddJingYuanCodexBlurtDrop</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -5095,6 +5996,711 @@
       <c r="N16" t="inlineStr">
         <is>
           <t>village_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>item_jingyuan_codex_orc</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexProgress</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>orc_common</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>j_drop_orc_common</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>orc_common</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>j_drop_orc_elite</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>orc_elite</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>j_drop_sign_aries</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>sign_aries</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>j_drop_sign_taurus</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>sign_taurus</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>j_drop_sign_gemini</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>sign_gemini</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>j_drop_sign_cancer</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>sign_cancer</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>j_drop_sign_leo</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>sign_leo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>j_drop_sign_virgo</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>sign_virgo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>j_drop_sign_libra</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>sign_libra</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>j_drop_sign_scorpio</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>sign_scorpio</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>j_drop_sign_sagittarius</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>sign_sagittarius</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>j_drop_sign_capricorn</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>sign_capricorn</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>j_drop_sign_aquarius</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>sign_aquarius</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>j_drop_sign_pisces</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>AddJingYuanCodexBlurtDrop</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>sign_pisces</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T182"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.375" customWidth="1" min="2" max="2"/>
@@ -2674,15 +2674,80 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>human_sword_lv1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1级剑</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HumanWeapon</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>human_sword_lv1</t>
+        </is>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>human_sword_lv1</t>
+          <t>human_lancer_lv1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1级剑</t>
+          <t>1级枪</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2698,7 +2763,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>human_sword_lv1</t>
+          <t>human_lancer_lv1</t>
         </is>
       </c>
       <c r="I26" t="b">
@@ -2742,28 +2807,28 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>human_lancer_lv1</t>
+          <t>small_knife</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1级枪</t>
+          <t>飞刀</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HumanWeapon</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>human_lancer_lv1</t>
+          <t>small_knife</t>
         </is>
       </c>
       <c r="I27" t="b">
@@ -2807,12 +2872,12 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>small_knife</t>
+          <t>smoke_grenade</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>飞刀</t>
+          <t>烟雾弹</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2824,11 +2889,11 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>small_knife</t>
+          <t>smoke_grenade</t>
         </is>
       </c>
       <c r="I28" t="b">
@@ -2865,39 +2930,99 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Consumable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sound_ball</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>声玉</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>sound_ball</t>
+        </is>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Consumable</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>smoke_grenade</t>
+          <t>desire_shard</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>烟雾弹</t>
+          <t>欲望碎片</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E30" t="b">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>smoke_grenade</t>
-        </is>
+        <v>999999</v>
       </c>
       <c r="I30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2927,42 +3052,32 @@
       </c>
       <c r="S30" t="b">
         <v>0</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>sound_ball</t>
+          <t>knowledge_shard</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>声玉</t>
+          <t>通识碎片</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E31" t="b">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>sound_ball</t>
-        </is>
+        <v>999999</v>
       </c>
       <c r="I31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2993,33 +3108,93 @@
       <c r="S31" t="b">
         <v>0</v>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>random_desire_crystal</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>随机欲望结晶</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>random_desire_crystal</t>
+        </is>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>desire_shard</t>
+          <t>desire_crystal_01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>欲望碎片</t>
+          <t>欲望结晶-1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>999999</v>
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>desire_crystal_01</t>
+        </is>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -3057,24 +3232,29 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>knowledge_shard</t>
+          <t>desire_crystal_02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>通识碎片</t>
+          <t>欲望结晶-2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>999999</v>
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>desire_crystal_02</t>
+        </is>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -3112,12 +3292,12 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>random_desire_crystal</t>
+          <t>desire_crystal_03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>随机欲望结晶</t>
+          <t>欲望结晶-3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3133,44 +3313,127 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>random_desire_crystal</t>
+          <t>desire_crystal_03</t>
         </is>
       </c>
       <c r="I35" t="b">
         <v>0</v>
       </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
       <c r="S35" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>desire_crystal_04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>欲望结晶-4</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>desire_crystal_04</t>
+        </is>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>desire_crystal_01</t>
+          <t>rumor_points</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>欲望结晶-1</t>
+          <t>秘闻</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>999999</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>desire_crystal_01</t>
+          <t>rumor_points</t>
         </is>
       </c>
       <c r="I37" t="b">
@@ -3209,32 +3472,27 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>desire_crystal_02</t>
+          <t>mind_shard_common</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>欲望结晶-2</t>
+          <t>心相碎片</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>desire_crystal_02</t>
-        </is>
+        <v>999999</v>
       </c>
       <c r="I38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3269,32 +3527,27 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>desire_crystal_03</t>
+          <t>mind_shard_rare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>欲望结晶-3</t>
+          <t>稀有心相碎片</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>desire_crystal_03</t>
-        </is>
+        <v>999999</v>
       </c>
       <c r="I39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3329,35 +3582,35 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>desire_crystal_04</t>
+          <t>part_mouth_lollipop</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>欲望结晶-4</t>
+          <t>棒棒糖环</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>PartGear</t>
         </is>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>desire_crystal_04</t>
+          <t>flower_01</t>
         </is>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3383,41 +3636,101 @@
         <v>0</v>
       </c>
       <c r="S40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>part_breast_brooch</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>感知胸针</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PartGear</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>flower_01</t>
+        </is>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="b">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>rumor_points</t>
+          <t>part_womb_bead</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>秘闻</t>
+          <t>温养念珠</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>PartGear</t>
         </is>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>999999</v>
+        <v>5</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>rumor_points</t>
+          <t>flower_01</t>
         </is>
       </c>
       <c r="I42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3449,87 +3762,215 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>mind_shard_common</t>
+          <t>part_tail_bell</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>心相碎片</t>
+          <t>尾铃</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>PartGear</t>
         </is>
       </c>
       <c r="E43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>999999</v>
+        <v>5</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>flower_01</t>
+        </is>
       </c>
       <c r="I43" t="b">
         <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="b">
+        <v>0</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>mind_shard_rare</t>
+          <t>mind_facet_01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>稀有心相碎片</t>
+          <t>酣眠</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>MindFacet</t>
         </is>
       </c>
       <c r="E44" t="b">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>999999</v>
+        <v>9999</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>mind_facet_01</t>
+        </is>
       </c>
       <c r="I44" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="b">
+        <v>0</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mind_facet_02</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>一晌贪欢</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>MindFacet</t>
+        </is>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>mind_facet_01</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="b">
+        <v>0</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>part_mouth_lollipop</t>
+          <t>mind_facet_03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>棒棒糖环</t>
+          <t>灯影</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>PartGear</t>
+          <t>MindFacet</t>
         </is>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>9999</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>flower_01</t>
+          <t>mind_facet_01</t>
         </is>
       </c>
       <c r="I46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3546,6 +3987,9 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="b">
@@ -3558,35 +4002,35 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>part_breast_brooch</t>
+          <t>mind_facet_04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>感知胸针</t>
+          <t>幽闭之间</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PartGear</t>
+          <t>MindFacet</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>9999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>flower_01</t>
+          <t>mind_facet_01</t>
         </is>
       </c>
       <c r="I47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3603,6 +4047,9 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="b">
@@ -3615,35 +4062,35 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>part_womb_bead</t>
+          <t>mind_facet_05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>温养念珠</t>
+          <t>燃烧</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PartGear</t>
+          <t>MindFacet</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>9999</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>flower_01</t>
+          <t>mind_facet_01</t>
         </is>
       </c>
       <c r="I48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3660,6 +4107,9 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="b">
@@ -3672,35 +4122,35 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>part_tail_bell</t>
+          <t>mind_facet_06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>尾铃</t>
+          <t>夜色</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PartGear</t>
+          <t>MindFacet</t>
         </is>
       </c>
       <c r="E49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>9999</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>flower_01</t>
+          <t>mind_facet_01</t>
         </is>
       </c>
       <c r="I49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3719,38 +4169,91 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
       <c r="R49" t="b">
         <v>0</v>
       </c>
       <c r="S49" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>rune_unlock_lady_up_1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E50" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>rune_unlock</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>mind_facet_01</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>酣眠</t>
+          <t>rune_unlock_lady_up_2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MindFacet</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>9999</v>
+        <v>0</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>mind_facet_01</t>
+          <t>rune_unlock</t>
         </is>
       </c>
       <c r="I51" t="b">
@@ -3783,38 +4286,38 @@
         <v>0</v>
       </c>
       <c r="S51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>mind_facet_02</t>
+          <t>quest_mat_herb</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>一晌贪欢</t>
+          <t>草药</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MindFacet</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E52" t="b">
         <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>mind_facet_01</t>
+          <t>stick</t>
         </is>
       </c>
       <c r="I52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3849,32 +4352,32 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>mind_facet_03</t>
+          <t>quest_mat_wood</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>灯影</t>
+          <t>木材</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>MindFacet</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E53" t="b">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>mind_facet_01</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="I53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3909,29 +4412,24 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>mind_facet_04</t>
+          <t>quest_control_village01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>幽闭之间</t>
+          <t>村子影响力</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MindFacet</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E54" t="b">
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>9999</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>mind_facet_01</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -3960,41 +4458,41 @@
         <v>0</v>
       </c>
       <c r="R54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>mind_facet_05</t>
+          <t>item_jingyuan_codex_orc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>燃烧</t>
+          <t>兽人精元样本</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MindFacet</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E55" t="b">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>mind_facet_01</t>
+          <t>item_jingyuan_codex_orc</t>
         </is>
       </c>
       <c r="I55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4023,38 +4521,38 @@
         <v>0</v>
       </c>
       <c r="S55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>mind_facet_06</t>
+          <t>j_drop_orc_common</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>夜色</t>
+          <t>兽人精元滴</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>MindFacet</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E56" t="b">
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>9999</v>
+        <v>99</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>mind_facet_01</t>
+          <t>j_drop_orc_common</t>
         </is>
       </c>
       <c r="I56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4080,16 +4578,81 @@
         <v>0</v>
       </c>
       <c r="R56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>j_drop_orc_elite</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>兽人精英精元滴</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>99</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>j_drop_orc_elite</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>rune_unlock_lady_up_1</t>
+          <t>j_drop_sign_aries</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sign_aries滴</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4100,13 +4663,16 @@
       <c r="E58" t="b">
         <v>0</v>
       </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>rune_unlock</t>
+          <t>j_drop_sign_aries</t>
         </is>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4132,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="R58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="b">
         <v>1</v>
@@ -4141,7 +4707,12 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>rune_unlock_lady_up_2</t>
+          <t>j_drop_sign_taurus</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sign_taurus滴</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4152,13 +4723,16 @@
       <c r="E59" t="b">
         <v>0</v>
       </c>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>rune_unlock</t>
+          <t>j_drop_sign_taurus</t>
         </is>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -4184,7 +4758,7 @@
         <v>0</v>
       </c>
       <c r="R59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" t="b">
         <v>1</v>
@@ -4193,12 +4767,12 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>quest_mat_herb</t>
+          <t>j_drop_sign_gemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>草药（占位）</t>
+          <t>sign_gemini滴</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4207,14 +4781,14 @@
         </is>
       </c>
       <c r="E60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stick</t>
+          <t>j_drop_sign_gemini</t>
         </is>
       </c>
       <c r="I60" t="b">
@@ -4244,21 +4818,21 @@
         <v>0</v>
       </c>
       <c r="R60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>quest_mat_wood</t>
+          <t>j_drop_sign_cancer</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>木材（占位）</t>
+          <t>sign_cancer滴</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4267,14 +4841,14 @@
         </is>
       </c>
       <c r="E61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>j_drop_sign_cancer</t>
         </is>
       </c>
       <c r="I61" t="b">
@@ -4304,27 +4878,63 @@
         <v>0</v>
       </c>
       <c r="R61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>quest_control_village01</t>
+          <t>j_drop_sign_leo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>村子影响力</t>
+          <t>sign_leo滴</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Normal</t>
         </is>
       </c>
       <c r="E62" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>j_drop_sign_leo</t>
+        </is>
       </c>
       <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="b">
@@ -4337,12 +4947,12 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>item_jingyuan_codex_orc</t>
+          <t>j_drop_sign_virgo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>兽人精元样本</t>
+          <t>sign_virgo滴</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4351,14 +4961,14 @@
         </is>
       </c>
       <c r="E63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>item_jingyuan_codex_orc</t>
+          <t>j_drop_sign_virgo</t>
         </is>
       </c>
       <c r="I63" t="b">
@@ -4388,21 +4998,81 @@
         <v>0</v>
       </c>
       <c r="R63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>j_drop_sign_libra</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sign_libra滴</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E64" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>j_drop_sign_libra</t>
+        </is>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="b">
+        <v>1</v>
+      </c>
+      <c r="S64" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>j_drop_orc_common</t>
+          <t>j_drop_sign_scorpio</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>兽人精元滴</t>
+          <t>sign_scorpio滴</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4411,14 +5081,14 @@
         </is>
       </c>
       <c r="E65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>j_drop_orc_common</t>
+          <t>j_drop_sign_scorpio</t>
         </is>
       </c>
       <c r="I65" t="b">
@@ -4457,12 +5127,12 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>j_drop_orc_elite</t>
+          <t>j_drop_sign_sagittarius</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>兽人精英精元滴</t>
+          <t>sign_sagittarius滴</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4471,14 +5141,14 @@
         </is>
       </c>
       <c r="E66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>j_drop_orc_elite</t>
+          <t>j_drop_sign_sagittarius</t>
         </is>
       </c>
       <c r="I66" t="b">
@@ -4517,12 +5187,12 @@
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>j_drop_sign_aries</t>
+          <t>j_drop_sign_capricorn</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sign_aries滴</t>
+          <t>sign_capricorn滴</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4538,7 +5208,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>j_drop_sign_aries</t>
+          <t>j_drop_sign_capricorn</t>
         </is>
       </c>
       <c r="I67" t="b">
@@ -4577,12 +5247,12 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>j_drop_sign_taurus</t>
+          <t>j_drop_sign_aquarius</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sign_taurus滴</t>
+          <t>sign_aquarius滴</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4598,7 +5268,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>j_drop_sign_taurus</t>
+          <t>j_drop_sign_aquarius</t>
         </is>
       </c>
       <c r="I68" t="b">
@@ -4637,12 +5307,12 @@
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>j_drop_sign_gemini</t>
+          <t>j_drop_sign_pisces</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sign_gemini滴</t>
+          <t>sign_pisces滴</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4658,7 +5328,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>j_drop_sign_gemini</t>
+          <t>j_drop_sign_pisces</t>
         </is>
       </c>
       <c r="I69" t="b">
@@ -4697,12 +5367,12 @@
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>j_drop_sign_cancer</t>
+          <t>wood_board</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sign_cancer滴</t>
+          <t>木板</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4711,14 +5381,19 @@
         </is>
       </c>
       <c r="E70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>material|wood</t>
+        </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>j_drop_sign_cancer</t>
+          <t>wood_board</t>
         </is>
       </c>
       <c r="I70" t="b">
@@ -4748,21 +5423,21 @@
         <v>0</v>
       </c>
       <c r="R70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>j_drop_sign_leo</t>
+          <t>mat_softwood_log</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sign_leo滴</t>
+          <t>软木原木</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4771,14 +5446,19 @@
         </is>
       </c>
       <c r="E71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>material|wood|big</t>
+        </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>j_drop_sign_leo</t>
+          <t>mat_softwood_log</t>
         </is>
       </c>
       <c r="I71" t="b">
@@ -4808,21 +5488,21 @@
         <v>0</v>
       </c>
       <c r="R71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>j_drop_sign_virgo</t>
+          <t>mat_hardwood_log</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sign_virgo滴</t>
+          <t>硬木原木</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4831,21 +5511,26 @@
         </is>
       </c>
       <c r="E72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>material|wood|big</t>
+        </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>j_drop_sign_virgo</t>
+          <t>mat_hardwood_log</t>
         </is>
       </c>
       <c r="I72" t="b">
         <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4868,21 +5553,21 @@
         <v>0</v>
       </c>
       <c r="R72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>j_drop_sign_libra</t>
+          <t>mat_seasoned_plank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sign_libra滴</t>
+          <t>干燥木板</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4891,21 +5576,26 @@
         </is>
       </c>
       <c r="E73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>material|wood</t>
+        </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>j_drop_sign_libra</t>
+          <t>mat_seasoned_plank</t>
         </is>
       </c>
       <c r="I73" t="b">
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4928,21 +5618,21 @@
         <v>0</v>
       </c>
       <c r="R73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>j_drop_sign_scorpio</t>
+          <t>mat_ironwood</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sign_scorpio滴</t>
+          <t>铁木</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4951,21 +5641,26 @@
         </is>
       </c>
       <c r="E74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>material|wood|big</t>
+        </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>j_drop_sign_scorpio</t>
+          <t>mat_ironwood</t>
         </is>
       </c>
       <c r="I74" t="b">
         <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4988,21 +5683,21 @@
         <v>0</v>
       </c>
       <c r="R74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>j_drop_sign_sagittarius</t>
+          <t>mat_spiritwood</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sign_sagittarius滴</t>
+          <t>灵木</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5011,21 +5706,26 @@
         </is>
       </c>
       <c r="E75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>material|wood|magic|big</t>
+        </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>j_drop_sign_sagittarius</t>
+          <t>mat_spiritwood</t>
         </is>
       </c>
       <c r="I75" t="b">
         <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5048,21 +5748,21 @@
         <v>0</v>
       </c>
       <c r="R75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>j_drop_sign_capricorn</t>
+          <t>mat_moonwood</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sign_capricorn滴</t>
+          <t>月纹木</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5071,21 +5771,26 @@
         </is>
       </c>
       <c r="E76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>material|wood|magic|big</t>
+        </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>j_drop_sign_capricorn</t>
+          <t>mat_moonwood</t>
         </is>
       </c>
       <c r="I76" t="b">
         <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5108,21 +5813,21 @@
         <v>0</v>
       </c>
       <c r="R76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>j_drop_sign_aquarius</t>
+          <t>mat_resin</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sign_aquarius滴</t>
+          <t>树脂</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5131,14 +5836,19 @@
         </is>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>material|alchemy</t>
+        </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>j_drop_sign_aquarius</t>
+          <t>mat_resin</t>
         </is>
       </c>
       <c r="I77" t="b">
@@ -5168,21 +5878,21 @@
         <v>0</v>
       </c>
       <c r="R77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>j_drop_sign_pisces</t>
+          <t>mat_charcoal</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sign_pisces滴</t>
+          <t>木炭</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5191,14 +5901,19 @@
         </is>
       </c>
       <c r="E78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>99</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>material|fuel</t>
+        </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>j_drop_sign_pisces</t>
+          <t>mat_charcoal</t>
         </is>
       </c>
       <c r="I78" t="b">
@@ -5228,10 +5943,6770 @@
         <v>0</v>
       </c>
       <c r="R78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>mat_plant_fiber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>植物纤维</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E79" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>99</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>material|fiber</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>mat_plant_fiber</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="b">
+        <v>0</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>mat_fieldstone</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>杂石</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>99</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>material|stone|big</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>mat_fieldstone</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="b">
+        <v>0</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>mat_limestone</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>石灰岩</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>99</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>material|stone|big</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>mat_limestone</t>
+        </is>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="b">
+        <v>0</v>
+      </c>
+      <c r="S81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>mat_granite</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>花岗岩</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>80</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>material|stone|big</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>mat_granite</t>
+        </is>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="b">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="b">
+        <v>0</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>mat_marble</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>大理石</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>40</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>material|stone|big</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>mat_marble</t>
+        </is>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="b">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="b">
+        <v>0</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>mat_obsidian</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>黑曜石</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>40</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>material|stone|glass</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>mat_obsidian</t>
+        </is>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="b">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="b">
+        <v>0</v>
+      </c>
+      <c r="S84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>mat_runed_stone</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>符刻石</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>20</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>material|stone|magic|big</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>mat_runed_stone</t>
+        </is>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="b">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="b">
+        <v>0</v>
+      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>mat_clay</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>黏土</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>99</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>material|clay</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>mat_clay</t>
+        </is>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="b">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="b">
+        <v>0</v>
+      </c>
+      <c r="S86" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>mat_brick</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>砖块</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E87" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>99</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>material|stone|ceramic|big</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>mat_brick</t>
+        </is>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="b">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="b">
+        <v>0</v>
+      </c>
+      <c r="S87" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>mat_sand</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>细沙</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>99</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>material|glass</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>mat_sand</t>
+        </is>
+      </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="b">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="b">
+        <v>0</v>
+      </c>
+      <c r="S88" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>mat_quartz_sand</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>石英砂</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E89" t="b">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>99</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>material|glass</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>mat_quartz_sand</t>
+        </is>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="b">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="b">
+        <v>0</v>
+      </c>
+      <c r="S89" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>mat_glass_shard</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>玻璃碎片</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>99</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>material|glass</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>mat_glass_shard</t>
+        </is>
+      </c>
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="b">
+        <v>0</v>
+      </c>
+      <c r="S90" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>mat_glass_pane</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>玻璃板</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E91" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" t="n">
+        <v>50</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>material|glass</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>mat_glass_pane</t>
+        </is>
+      </c>
+      <c r="I91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="b">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="b">
+        <v>0</v>
+      </c>
+      <c r="S91" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>mat_colored_glass</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>彩色玻璃</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>40</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>material|glass|luxury</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>mat_colored_glass</t>
+        </is>
+      </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="b">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="b">
+        <v>0</v>
+      </c>
+      <c r="S92" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>mat_crystal_lens</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>水晶透镜</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E93" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>20</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>material|glass|craft</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>mat_crystal_lens</t>
+        </is>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="b">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="b">
+        <v>0</v>
+      </c>
+      <c r="S93" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>mat_alchemical_glass</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>炼金玻璃</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E94" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>20</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>material|glass|alchemy|magic</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>mat_alchemical_glass</t>
+        </is>
+      </c>
+      <c r="I94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>3</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="b">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="b">
+        <v>0</v>
+      </c>
+      <c r="S94" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>mat_copper_ore</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>铜矿石</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>99</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>material|ore|big</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>mat_copper_ore</t>
+        </is>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="b">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="b">
+        <v>0</v>
+      </c>
+      <c r="S95" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>mat_tin_ore</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>锡矿石</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="n">
+        <v>99</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>material|ore|big</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>mat_tin_ore</t>
+        </is>
+      </c>
+      <c r="I96" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="b">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="b">
+        <v>0</v>
+      </c>
+      <c r="S96" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>mat_iron_ore</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>铁矿石</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" t="n">
+        <v>99</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>material|ore|big</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>mat_iron_ore</t>
+        </is>
+      </c>
+      <c r="I97" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="b">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="b">
+        <v>0</v>
+      </c>
+      <c r="S97" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>mat_silver_ore</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>银矿石</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E98" t="b">
+        <v>1</v>
+      </c>
+      <c r="F98" t="n">
+        <v>60</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>material|ore|big</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>mat_silver_ore</t>
+        </is>
+      </c>
+      <c r="I98" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="b">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="b">
+        <v>0</v>
+      </c>
+      <c r="S98" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>mat_mana_ore</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>魔晶矿石</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+      <c r="F99" t="n">
+        <v>40</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>material|ore|magic|big</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>mat_mana_ore</t>
+        </is>
+      </c>
+      <c r="I99" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="b">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="b">
+        <v>0</v>
+      </c>
+      <c r="S99" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>mat_copper_ingot</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>铜锭</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E100" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>99</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>material|metal</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>mat_copper_ingot</t>
+        </is>
+      </c>
+      <c r="I100" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="b">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="b">
+        <v>0</v>
+      </c>
+      <c r="S100" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>mat_bronze_ingot</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>青铜锭</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>99</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>material|metal</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>mat_bronze_ingot</t>
+        </is>
+      </c>
+      <c r="I101" t="b">
+        <v>1</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="b">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="b">
+        <v>0</v>
+      </c>
+      <c r="S101" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>mat_iron_ingot</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>铁锭</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>99</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>material|metal</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>mat_iron_ingot</t>
+        </is>
+      </c>
+      <c r="I102" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="b">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="b">
+        <v>0</v>
+      </c>
+      <c r="S102" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>mat_steel_ingot</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>钢锭</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" t="n">
+        <v>80</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>material|metal</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>mat_steel_ingot</t>
+        </is>
+      </c>
+      <c r="I103" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="b">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="b">
+        <v>0</v>
+      </c>
+      <c r="S103" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>mat_silver_ingot</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>银锭</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" t="n">
+        <v>80</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>material|metal|precious</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>mat_silver_ingot</t>
+        </is>
+      </c>
+      <c r="I104" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="b">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="b">
+        <v>0</v>
+      </c>
+      <c r="S104" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>mat_mana_ingot</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>魔晶锭</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+      <c r="F105" t="n">
+        <v>40</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>material|metal|magic</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>mat_mana_ingot</t>
+        </is>
+      </c>
+      <c r="I105" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="b">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="b">
+        <v>0</v>
+      </c>
+      <c r="S105" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>mat_linen_thread</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>亚麻线</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E106" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" t="n">
+        <v>99</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>material|textile</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>mat_linen_thread</t>
+        </is>
+      </c>
+      <c r="I106" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="b">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="b">
+        <v>0</v>
+      </c>
+      <c r="S106" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>mat_linen_cloth</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>亚麻布</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E107" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" t="n">
+        <v>99</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>material|textile</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>mat_linen_cloth</t>
+        </is>
+      </c>
+      <c r="I107" t="b">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="b">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="b">
+        <v>0</v>
+      </c>
+      <c r="S107" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>mat_wool_fleece</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>羊毛</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E108" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" t="n">
+        <v>99</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>material|textile</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>mat_wool_fleece</t>
+        </is>
+      </c>
+      <c r="I108" t="b">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="b">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="b">
+        <v>0</v>
+      </c>
+      <c r="S108" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>mat_wool_cloth</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>呢布</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E109" t="b">
+        <v>1</v>
+      </c>
+      <c r="F109" t="n">
+        <v>80</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>material|textile</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>mat_wool_cloth</t>
+        </is>
+      </c>
+      <c r="I109" t="b">
+        <v>1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="b">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="b">
+        <v>0</v>
+      </c>
+      <c r="S109" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>mat_cotton_cloth</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>棉布</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E110" t="b">
+        <v>1</v>
+      </c>
+      <c r="F110" t="n">
+        <v>80</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>material|textile</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>mat_cotton_cloth</t>
+        </is>
+      </c>
+      <c r="I110" t="b">
+        <v>1</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="b">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="b">
+        <v>0</v>
+      </c>
+      <c r="S110" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>mat_silk_thread</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>丝线</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E111" t="b">
+        <v>1</v>
+      </c>
+      <c r="F111" t="n">
+        <v>99</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>material|textile|luxury</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>mat_silk_thread</t>
+        </is>
+      </c>
+      <c r="I111" t="b">
+        <v>1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="b">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="b">
+        <v>0</v>
+      </c>
+      <c r="S111" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>mat_silk_bolt</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>丝绸</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E112" t="b">
+        <v>1</v>
+      </c>
+      <c r="F112" t="n">
+        <v>50</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>material|textile|luxury</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>mat_silk_bolt</t>
+        </is>
+      </c>
+      <c r="I112" t="b">
+        <v>1</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="b">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="b">
+        <v>0</v>
+      </c>
+      <c r="S112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>mat_dyed_cloth</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>染色布</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E113" t="b">
+        <v>1</v>
+      </c>
+      <c r="F113" t="n">
+        <v>80</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>material|textile</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>mat_dyed_cloth</t>
+        </is>
+      </c>
+      <c r="I113" t="b">
+        <v>1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="b">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="b">
+        <v>0</v>
+      </c>
+      <c r="S113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>mat_velvet</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>天鹅绒</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E114" t="b">
+        <v>1</v>
+      </c>
+      <c r="F114" t="n">
+        <v>40</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>material|textile|luxury</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>mat_velvet</t>
+        </is>
+      </c>
+      <c r="I114" t="b">
+        <v>1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="b">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="b">
+        <v>0</v>
+      </c>
+      <c r="S114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>mat_brocade</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>织锦</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E115" t="b">
+        <v>1</v>
+      </c>
+      <c r="F115" t="n">
+        <v>30</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>material|textile|luxury</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>mat_brocade</t>
+        </is>
+      </c>
+      <c r="I115" t="b">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
+        <v>3</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="b">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="b">
+        <v>0</v>
+      </c>
+      <c r="S115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>mat_rough_hide</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>粗皮</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E116" t="b">
+        <v>1</v>
+      </c>
+      <c r="F116" t="n">
+        <v>80</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>material|leather</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>mat_rough_hide</t>
+        </is>
+      </c>
+      <c r="I116" t="b">
+        <v>1</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="b">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="b">
+        <v>0</v>
+      </c>
+      <c r="S116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>mat_tanned_leather</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>鞣制皮革</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E117" t="b">
+        <v>1</v>
+      </c>
+      <c r="F117" t="n">
+        <v>80</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>material|leather</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>mat_tanned_leather</t>
+        </is>
+      </c>
+      <c r="I117" t="b">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="b">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="b">
+        <v>0</v>
+      </c>
+      <c r="S117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>mat_fine_leather</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>精制皮革</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E118" t="b">
+        <v>1</v>
+      </c>
+      <c r="F118" t="n">
+        <v>50</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>material|leather|luxury</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>mat_fine_leather</t>
+        </is>
+      </c>
+      <c r="I118" t="b">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>2</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="b">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="b">
+        <v>0</v>
+      </c>
+      <c r="S118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>mat_mageweave</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>魔纹布</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E119" t="b">
+        <v>1</v>
+      </c>
+      <c r="F119" t="n">
+        <v>30</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>material|textile|magic</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>mat_mageweave</t>
+        </is>
+      </c>
+      <c r="I119" t="b">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>3</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="b">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="b">
+        <v>0</v>
+      </c>
+      <c r="S119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>mat_beeswax</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>蜂蜡</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E120" t="b">
+        <v>1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>99</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>material|alchemy</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>mat_beeswax</t>
+        </is>
+      </c>
+      <c r="I120" t="b">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="b">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="b">
+        <v>0</v>
+      </c>
+      <c r="S120" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>mat_tallow</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>油脂</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E121" t="b">
+        <v>1</v>
+      </c>
+      <c r="F121" t="n">
+        <v>99</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>material|alchemy</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>mat_tallow</t>
+        </is>
+      </c>
+      <c r="I121" t="b">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="b">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="b">
+        <v>0</v>
+      </c>
+      <c r="S121" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>mat_bone</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>兽骨</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E122" t="b">
+        <v>1</v>
+      </c>
+      <c r="F122" t="n">
+        <v>99</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>material|bone</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>mat_bone</t>
+        </is>
+      </c>
+      <c r="I122" t="b">
+        <v>1</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="b">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="b">
+        <v>0</v>
+      </c>
+      <c r="S122" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>mat_bone_dust</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>骨粉</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E123" t="b">
+        <v>1</v>
+      </c>
+      <c r="F123" t="n">
+        <v>99</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>material|alchemy</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>mat_bone_dust</t>
+        </is>
+      </c>
+      <c r="I123" t="b">
+        <v>1</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="b">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="b">
+        <v>0</v>
+      </c>
+      <c r="S123" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>mat_sulfur</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>硫磺</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E124" t="b">
+        <v>1</v>
+      </c>
+      <c r="F124" t="n">
+        <v>80</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>material|alchemy</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>mat_sulfur</t>
+        </is>
+      </c>
+      <c r="I124" t="b">
+        <v>1</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="b">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="b">
+        <v>0</v>
+      </c>
+      <c r="S124" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>mat_saltpeter</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>硝石</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E125" t="b">
+        <v>1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>80</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>material|alchemy</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>mat_saltpeter</t>
+        </is>
+      </c>
+      <c r="I125" t="b">
+        <v>1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="b">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="b">
+        <v>0</v>
+      </c>
+      <c r="S125" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>mat_alum</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>明矾</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E126" t="b">
+        <v>1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>80</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>material|alchemy|dye</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>mat_alum</t>
+        </is>
+      </c>
+      <c r="I126" t="b">
+        <v>1</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="b">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="b">
+        <v>0</v>
+      </c>
+      <c r="S126" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>mat_lime</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>石灰</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E127" t="b">
+        <v>1</v>
+      </c>
+      <c r="F127" t="n">
+        <v>99</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>material|alchemy|stone</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>mat_lime</t>
+        </is>
+      </c>
+      <c r="I127" t="b">
+        <v>1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="b">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="b">
+        <v>0</v>
+      </c>
+      <c r="S127" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>mat_lamp_oil</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>灯油</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E128" t="b">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>99</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>material|fuel|alchemy</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>mat_lamp_oil</t>
+        </is>
+      </c>
+      <c r="I128" t="b">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="b">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="b">
+        <v>0</v>
+      </c>
+      <c r="S128" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>mat_hide_glue</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>皮胶</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E129" t="b">
+        <v>1</v>
+      </c>
+      <c r="F129" t="n">
+        <v>99</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>material|glue|alchemy</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>mat_hide_glue</t>
+        </is>
+      </c>
+      <c r="I129" t="b">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="b">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="b">
+        <v>0</v>
+      </c>
+      <c r="S129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>mat_natural_latex</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>天然胶乳</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E130" t="b">
+        <v>1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>60</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>material|latex|alchemy</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>mat_natural_latex</t>
+        </is>
+      </c>
+      <c r="I130" t="b">
+        <v>1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="b">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="b">
+        <v>0</v>
+      </c>
+      <c r="S130" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>mat_elastic_gum</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>弹性树胶</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E131" t="b">
+        <v>1</v>
+      </c>
+      <c r="F131" t="n">
+        <v>40</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>material|latex|alchemy|exotic</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>mat_elastic_gum</t>
+        </is>
+      </c>
+      <c r="I131" t="b">
+        <v>1</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="b">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="b">
+        <v>0</v>
+      </c>
+      <c r="S131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>mat_alchemical_rubber</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>炼金胶料</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E132" t="b">
+        <v>1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>30</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>material|latex|alchemy|magic</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>mat_alchemical_rubber</t>
+        </is>
+      </c>
+      <c r="I132" t="b">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="b">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="b">
+        <v>0</v>
+      </c>
+      <c r="S132" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>loot_rusty_nail</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>生锈铁钉</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E133" t="b">
+        <v>1</v>
+      </c>
+      <c r="F133" t="n">
+        <v>99</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>loot|metal</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>loot_rusty_nail</t>
+        </is>
+      </c>
+      <c r="I133" t="b">
+        <v>1</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="b">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="b">
+        <v>0</v>
+      </c>
+      <c r="S133" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>loot_bent_hinge</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>弯曲合页</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E134" t="b">
+        <v>1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>99</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>loot|metal</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>loot_bent_hinge</t>
+        </is>
+      </c>
+      <c r="I134" t="b">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="b">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="b">
+        <v>0</v>
+      </c>
+      <c r="S134" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>loot_broken_gear</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>破损齿轮</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E135" t="b">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>50</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>loot|metal|craft</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>loot_broken_gear</t>
+        </is>
+      </c>
+      <c r="I135" t="b">
+        <v>1</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="b">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="b">
+        <v>0</v>
+      </c>
+      <c r="S135" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>loot_cracked_cup</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>裂口陶杯</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E136" t="b">
+        <v>1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>50</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>loot|ceramic</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>loot_cracked_cup</t>
+        </is>
+      </c>
+      <c r="I136" t="b">
+        <v>1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="b">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="b">
+        <v>0</v>
+      </c>
+      <c r="S136" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>loot_empty_bottle</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>空玻璃瓶</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E137" t="b">
+        <v>1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>50</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>loot|glass</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>loot_empty_bottle</t>
+        </is>
+      </c>
+      <c r="I137" t="b">
+        <v>1</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="b">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="b">
+        <v>0</v>
+      </c>
+      <c r="S137" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>loot_candle_stub</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>残烛</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E138" t="b">
+        <v>1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>99</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>loot|alchemy</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>loot_candle_stub</t>
+        </is>
+      </c>
+      <c r="I138" t="b">
+        <v>1</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="b">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="b">
+        <v>0</v>
+      </c>
+      <c r="S138" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>loot_cloth_scrap</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>碎布片</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E139" t="b">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>99</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>loot|textile</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>loot_cloth_scrap</t>
+        </is>
+      </c>
+      <c r="I139" t="b">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="b">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="b">
+        <v>0</v>
+      </c>
+      <c r="S139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>loot_rope_end</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>短绳头</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E140" t="b">
+        <v>1</v>
+      </c>
+      <c r="F140" t="n">
+        <v>99</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>loot|fiber</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>loot_rope_end</t>
+        </is>
+      </c>
+      <c r="I140" t="b">
+        <v>1</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="b">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="b">
+        <v>0</v>
+      </c>
+      <c r="S140" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>loot_torn_page</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>残破书页</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E141" t="b">
+        <v>1</v>
+      </c>
+      <c r="F141" t="n">
+        <v>99</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>loot|paper</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>loot_torn_page</t>
+        </is>
+      </c>
+      <c r="I141" t="b">
+        <v>1</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="b">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="b">
+        <v>0</v>
+      </c>
+      <c r="S141" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>loot_wax_seal</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>旧蜡封</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E142" t="b">
+        <v>1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>50</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>loot|paper|alchemy</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>loot_wax_seal</t>
+        </is>
+      </c>
+      <c r="I142" t="b">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="b">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="b">
+        <v>0</v>
+      </c>
+      <c r="S142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>loot_old_coin</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>旧钱币</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E143" t="b">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>99</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>loot|precious</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>loot_old_coin</t>
+        </is>
+      </c>
+      <c r="I143" t="b">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="b">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="b">
+        <v>0</v>
+      </c>
+      <c r="S143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>loot_spice_pinch</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>香料撮</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E144" t="b">
+        <v>1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>50</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>loot|food|alchemy</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>loot_spice_pinch</t>
+        </is>
+      </c>
+      <c r="I144" t="b">
+        <v>1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="b">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="b">
+        <v>0</v>
+      </c>
+      <c r="S144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>loot_key_blank</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>钥匙坯</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E145" t="b">
+        <v>1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>50</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>loot|metal|craft</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>loot_key_blank</t>
+        </is>
+      </c>
+      <c r="I145" t="b">
+        <v>1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="b">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="b">
+        <v>0</v>
+      </c>
+      <c r="S145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>loot_chipped_gem</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>缺角宝石</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E146" t="b">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>30</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>loot|precious|craft</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>loot_chipped_gem</t>
+        </is>
+      </c>
+      <c r="I146" t="b">
+        <v>1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="b">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="b">
+        <v>0</v>
+      </c>
+      <c r="S146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>loot_bone_charm</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>骨制护符</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E147" t="b">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>30</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>loot|bone|magic</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>loot_bone_charm</t>
+        </is>
+      </c>
+      <c r="I147" t="b">
+        <v>1</v>
+      </c>
+      <c r="J147" t="n">
+        <v>2</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="b">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="b">
+        <v>0</v>
+      </c>
+      <c r="S147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>loot_broken_lens</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>破裂透镜</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E148" t="b">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>30</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>loot|glass|craft</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>loot_broken_lens</t>
+        </is>
+      </c>
+      <c r="I148" t="b">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="b">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="b">
+        <v>0</v>
+      </c>
+      <c r="S148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>mat_alchemical_gel</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>炼金凝胶</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E149" t="b">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>80</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>material|alchemy|gel</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>mat_alchemical_gel</t>
+        </is>
+      </c>
+      <c r="I149" t="b">
+        <v>1</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="b">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="b">
+        <v>0</v>
+      </c>
+      <c r="S149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>mat_mana_shard</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>玛娜碎晶</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E150" t="b">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>99</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>material|crystal|magic</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>mat_mana_shard</t>
+        </is>
+      </c>
+      <c r="I150" t="b">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="b">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="b">
+        <v>0</v>
+      </c>
+      <c r="S150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>mat_mana_crystal</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>玛娜晶体</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E151" t="b">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>60</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>material|crystal|magic</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>mat_mana_crystal</t>
+        </is>
+      </c>
+      <c r="I151" t="b">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>2</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="b">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="b">
+        <v>0</v>
+      </c>
+      <c r="S151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>mat_mana_storage_core</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>蓄魔晶芯</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E152" t="b">
+        <v>1</v>
+      </c>
+      <c r="F152" t="n">
+        <v>20</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>material|crystal|magic|craft</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>mat_mana_storage_core</t>
+        </is>
+      </c>
+      <c r="I152" t="b">
+        <v>1</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="b">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="b">
+        <v>0</v>
+      </c>
+      <c r="S152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>mat_conductive_copper_wire</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>导魔铜丝</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E153" t="b">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>80</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>material|metal|magic|craft</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>mat_conductive_copper_wire</t>
+        </is>
+      </c>
+      <c r="I153" t="b">
+        <v>1</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="b">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="b">
+        <v>0</v>
+      </c>
+      <c r="S153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>mat_arcane_copper_plate</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>符纹铜片</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E154" t="b">
+        <v>1</v>
+      </c>
+      <c r="F154" t="n">
+        <v>80</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>material|metal|magic|craft</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>mat_arcane_copper_plate</t>
+        </is>
+      </c>
+      <c r="I154" t="b">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="b">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="b">
+        <v>0</v>
+      </c>
+      <c r="S154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>mat_insulating_ceramic</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>绝魔瓷片</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E155" t="b">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
+        <v>50</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>material|ceramic|magic|craft</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>mat_insulating_ceramic</t>
+        </is>
+      </c>
+      <c r="I155" t="b">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>2</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="b">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="b">
+        <v>0</v>
+      </c>
+      <c r="S155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>mat_switch_rune_plate</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>启魔符片</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E156" t="b">
+        <v>1</v>
+      </c>
+      <c r="F156" t="n">
+        <v>50</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>material|stone|magic|craft</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>mat_switch_rune_plate</t>
+        </is>
+      </c>
+      <c r="I156" t="b">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>2</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="b">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="b">
+        <v>0</v>
+      </c>
+      <c r="S156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>mat_lantern_wax</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>灯烛蜡</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E157" t="b">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>99</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>material|wax</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>mat_lantern_wax</t>
+        </is>
+      </c>
+      <c r="I157" t="b">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="b">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="b">
+        <v>0</v>
+      </c>
+      <c r="S157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>mat_sealing_wax</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>封印蜡</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E158" t="b">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>80</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>material|wax|alchemy</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>mat_sealing_wax</t>
+        </is>
+      </c>
+      <c r="I158" t="b">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="b">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="b">
+        <v>0</v>
+      </c>
+      <c r="S158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>mat_polishing_wax</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>抛光蜡</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E159" t="b">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>80</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>material|wax|craft</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>mat_polishing_wax</t>
+        </is>
+      </c>
+      <c r="I159" t="b">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
+        <v>1</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="b">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="b">
+        <v>0</v>
+      </c>
+      <c r="S159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>mat_warding_wax</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>避魔蜡</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E160" t="b">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>60</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>material|wax|magic|alchemy</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>mat_warding_wax</t>
+        </is>
+      </c>
+      <c r="I160" t="b">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>2</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="b">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="b">
+        <v>0</v>
+      </c>
+      <c r="S160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>mat_preserving_wax</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>防腐蜡</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E161" t="b">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>60</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>material|wax|alchemy</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>mat_preserving_wax</t>
+        </is>
+      </c>
+      <c r="I161" t="b">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>2</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="b">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="b">
+        <v>0</v>
+      </c>
+      <c r="S161" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>loot_painted_wooden_doll</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>彩绘木偶</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E162" t="b">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>20</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>loot|craft|toy</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>loot_painted_wooden_doll</t>
+        </is>
+      </c>
+      <c r="I162" t="b">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="b">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="b">
+        <v>0</v>
+      </c>
+      <c r="S162" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>loot_tin_knight_figure</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>锡铸骑士</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E163" t="b">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>20</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>loot|craft|toy|metal</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>loot_tin_knight_figure</t>
+        </is>
+      </c>
+      <c r="I163" t="b">
+        <v>1</v>
+      </c>
+      <c r="J163" t="n">
+        <v>1</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="b">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="b">
+        <v>0</v>
+      </c>
+      <c r="S163" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>loot_bone_chess_piece</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>骨雕棋子</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E164" t="b">
+        <v>1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>30</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>loot|craft|toy|bone</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>loot_bone_chess_piece</t>
+        </is>
+      </c>
+      <c r="I164" t="b">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="b">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="b">
+        <v>0</v>
+      </c>
+      <c r="S164" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>loot_illustrated_cards</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>手绘纸牌</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E165" t="b">
+        <v>1</v>
+      </c>
+      <c r="F165" t="n">
+        <v>20</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>loot|craft|toy|paper</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>loot_illustrated_cards</t>
+        </is>
+      </c>
+      <c r="I165" t="b">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="b">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="b">
+        <v>0</v>
+      </c>
+      <c r="S165" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>loot_miniature_ship</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>微缩帆船</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E166" t="b">
+        <v>1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>10</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>loot|craft|toy|decor</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>loot_miniature_ship</t>
+        </is>
+      </c>
+      <c r="I166" t="b">
+        <v>1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>2</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="b">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="b">
+        <v>0</v>
+      </c>
+      <c r="S166" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>loot_glass_wind_chime</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>玻璃风铃</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E167" t="b">
+        <v>1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>10</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>loot|craft|glass|decor</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>loot_glass_wind_chime</t>
+        </is>
+      </c>
+      <c r="I167" t="b">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>2</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="b">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="b">
+        <v>0</v>
+      </c>
+      <c r="S167" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>loot_enameled_cup</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>彩釉小杯</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E168" t="b">
+        <v>1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>20</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>loot|craft|ceramic|home</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>loot_enameled_cup</t>
+        </is>
+      </c>
+      <c r="I168" t="b">
+        <v>1</v>
+      </c>
+      <c r="J168" t="n">
+        <v>1</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="b">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="b">
+        <v>0</v>
+      </c>
+      <c r="S168" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>loot_carved_spice_box</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>雕花香料匣</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E169" t="b">
+        <v>1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>10</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>loot|craft|wood|home</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>loot_carved_spice_box</t>
+        </is>
+      </c>
+      <c r="I169" t="b">
+        <v>1</v>
+      </c>
+      <c r="J169" t="n">
+        <v>2</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="b">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="b">
+        <v>0</v>
+      </c>
+      <c r="S169" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>loot_silver_candlestick</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>银饰烛台</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E170" t="b">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>10</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>loot|craft|metal|home|luxury</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>loot_silver_candlestick</t>
+        </is>
+      </c>
+      <c r="I170" t="b">
+        <v>1</v>
+      </c>
+      <c r="J170" t="n">
+        <v>2</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="b">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="R170" t="b">
+        <v>0</v>
+      </c>
+      <c r="S170" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>loot_embroidery_pillow</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>刺绣靠枕</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E171" t="b">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>20</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>loot|craft|textile|home</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>loot_embroidery_pillow</t>
+        </is>
+      </c>
+      <c r="I171" t="b">
+        <v>1</v>
+      </c>
+      <c r="J171" t="n">
+        <v>1</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="b">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="b">
+        <v>0</v>
+      </c>
+      <c r="S171" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>loot_lacquered_tray</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>漆绘托盘</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E172" t="b">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>10</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>loot|craft|wood|home|luxury</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>loot_lacquered_tray</t>
+        </is>
+      </c>
+      <c r="I172" t="b">
+        <v>1</v>
+      </c>
+      <c r="J172" t="n">
+        <v>2</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="b">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="R172" t="b">
+        <v>0</v>
+      </c>
+      <c r="S172" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>loot_brass_inkwell</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>黄铜墨水瓶</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E173" t="b">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>20</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>loot|craft|metal|study</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>loot_brass_inkwell</t>
+        </is>
+      </c>
+      <c r="I173" t="b">
+        <v>1</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="b">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" t="b">
+        <v>0</v>
+      </c>
+      <c r="S173" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>loot_stained_glass_icon</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>彩玻小圣像</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E174" t="b">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>8</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>loot|craft|glass|decor|magic</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>loot_stained_glass_icon</t>
+        </is>
+      </c>
+      <c r="I174" t="b">
+        <v>1</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="b">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="b">
+        <v>0</v>
+      </c>
+      <c r="S174" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>loot_porcelain_mask</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>瓷制假面</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E175" t="b">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>10</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>loot|craft|ceramic|decor</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>loot_porcelain_mask</t>
+        </is>
+      </c>
+      <c r="I175" t="b">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>2</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="b">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="R175" t="b">
+        <v>0</v>
+      </c>
+      <c r="S175" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>loot_table_astrolabe</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>桌上星盘</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E176" t="b">
+        <v>1</v>
+      </c>
+      <c r="F176" t="n">
+        <v>8</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>loot|craft|metal|study|magic</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>loot_table_astrolabe</t>
+        </is>
+      </c>
+      <c r="I176" t="b">
+        <v>1</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="b">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="b">
+        <v>0</v>
+      </c>
+      <c r="S176" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>loot_blessing_wall_charm</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>祈福挂饰</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E177" t="b">
+        <v>1</v>
+      </c>
+      <c r="F177" t="n">
+        <v>20</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>loot|craft|decor|magic</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>loot_blessing_wall_charm</t>
+        </is>
+      </c>
+      <c r="I177" t="b">
+        <v>1</v>
+      </c>
+      <c r="J177" t="n">
+        <v>2</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="b">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="b">
+        <v>0</v>
+      </c>
+      <c r="S177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>loot_scripture_copy</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>经文抄本</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E178" t="b">
+        <v>1</v>
+      </c>
+      <c r="F178" t="n">
+        <v>20</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>loot|craft|paper|church</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>loot_scripture_copy</t>
+        </is>
+      </c>
+      <c r="I178" t="b">
+        <v>1</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="b">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="R178" t="b">
+        <v>0</v>
+      </c>
+      <c r="S178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>loot_illuminated_prayer_book</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>彩饰祈祷书</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E179" t="b">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>10</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>loot|craft|paper|church|luxury</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>loot_illuminated_prayer_book</t>
+        </is>
+      </c>
+      <c r="I179" t="b">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>2</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="b">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="R179" t="b">
+        <v>0</v>
+      </c>
+      <c r="S179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>loot_blessed_prayer_beads</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>祝圣念珠</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E180" t="b">
+        <v>1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>20</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>loot|craft|church|magic</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>loot_blessed_prayer_beads</t>
+        </is>
+      </c>
+      <c r="I180" t="b">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>2</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="b">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="R180" t="b">
+        <v>0</v>
+      </c>
+      <c r="S180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>loot_incense_censer</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>熏香吊炉</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E181" t="b">
+        <v>1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>10</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>loot|craft|metal|church</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>loot_incense_censer</t>
+        </is>
+      </c>
+      <c r="I181" t="b">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>2</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="b">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" t="b">
+        <v>0</v>
+      </c>
+      <c r="S181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>loot_silver_reliquary</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>银制圣匣</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E182" t="b">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>8</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>loot|craft|metal|church|luxury|magic</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>loot_silver_reliquary</t>
+        </is>
+      </c>
+      <c r="I182" t="b">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="b">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="R182" t="b">
+        <v>0</v>
+      </c>
+      <c r="S182" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5691,7 +13166,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" t="n">
         <v>4</v>
@@ -5866,7 +13340,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" t="n">
         <v>11</v>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T182"/>
+  <dimension ref="A1:T194"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13.375" customWidth="1" min="2" max="2"/>
@@ -12707,6 +12707,846 @@
       </c>
       <c r="S182" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>furn_oak_refectory_table</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>橡木长餐桌</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E183" t="b">
+        <v>0</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>furniture|home|wood</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>furn_oak_refectory_table</t>
+        </is>
+      </c>
+      <c r="I183" t="b">
+        <v>1</v>
+      </c>
+      <c r="J183" t="n">
+        <v>1</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="b">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="b">
+        <v>0</v>
+      </c>
+      <c r="S183" t="b">
+        <v>0</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>furn_walnut_carved_chair</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>胡桃木雕花椅</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E184" t="b">
+        <v>0</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>furniture|home|wood</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>furn_walnut_carved_chair</t>
+        </is>
+      </c>
+      <c r="I184" t="b">
+        <v>1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>1</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="b">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="b">
+        <v>0</v>
+      </c>
+      <c r="S184" t="b">
+        <v>0</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>furn_velvet_canopy_bed</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>天鹅绒帷幔床</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E185" t="b">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>furniture|home|textile|luxury</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>furn_velvet_canopy_bed</t>
+        </is>
+      </c>
+      <c r="I185" t="b">
+        <v>1</v>
+      </c>
+      <c r="J185" t="n">
+        <v>2</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="b">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="b">
+        <v>0</v>
+      </c>
+      <c r="S185" t="b">
+        <v>0</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>furn_brass_candle_chandelier</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>黄铜烛火吊灯</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E186" t="b">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>furniture|home|metal|light</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>furn_brass_candle_chandelier</t>
+        </is>
+      </c>
+      <c r="I186" t="b">
+        <v>1</v>
+      </c>
+      <c r="J186" t="n">
+        <v>1</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="b">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="b">
+        <v>0</v>
+      </c>
+      <c r="S186" t="b">
+        <v>0</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>furn_stained_glass_lamp</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>彩绘玻璃魔灯</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E187" t="b">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>furniture|home|glass|magic|light</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>furn_stained_glass_lamp</t>
+        </is>
+      </c>
+      <c r="I187" t="b">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>2</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="b">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="b">
+        <v>0</v>
+      </c>
+      <c r="S187" t="b">
+        <v>0</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>furn_marble_washstand</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>大理石盥洗台</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E188" t="b">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>furniture|home|stone|luxury</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>furn_marble_washstand</t>
+        </is>
+      </c>
+      <c r="I188" t="b">
+        <v>1</v>
+      </c>
+      <c r="J188" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="b">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="b">
+        <v>0</v>
+      </c>
+      <c r="S188" t="b">
+        <v>0</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>furn_alchemist_cabinet</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>炼金药剂柜</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E189" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>furniture|home|alchemy|craft</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>furn_alchemist_cabinet</t>
+        </is>
+      </c>
+      <c r="I189" t="b">
+        <v>1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>2</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="b">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="b">
+        <v>0</v>
+      </c>
+      <c r="S189" t="b">
+        <v>0</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>furn_astrologer_writing_desk</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>占星师书写桌</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E190" t="b">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>furniture|home|study|magic</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>furn_astrologer_writing_desk</t>
+        </is>
+      </c>
+      <c r="I190" t="b">
+        <v>1</v>
+      </c>
+      <c r="J190" t="n">
+        <v>2</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="b">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="b">
+        <v>0</v>
+      </c>
+      <c r="S190" t="b">
+        <v>0</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>furn_runed_bookshelf</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>符刻藏书架</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E191" t="b">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>furniture|home|study|magic|wood</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>furn_runed_bookshelf</t>
+        </is>
+      </c>
+      <c r="I191" t="b">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>2</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="b">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="b">
+        <v>0</v>
+      </c>
+      <c r="S191" t="b">
+        <v>0</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>furn_gilded_room_divider</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>镏金折屏</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E192" t="b">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>furniture|home|decor|luxury</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>furn_gilded_room_divider</t>
+        </is>
+      </c>
+      <c r="I192" t="b">
+        <v>1</v>
+      </c>
+      <c r="J192" t="n">
+        <v>2</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="b">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="b">
+        <v>0</v>
+      </c>
+      <c r="S192" t="b">
+        <v>0</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>furn_moonwood_vanity</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>月纹木梳妆台</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E193" t="b">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>furniture|home|magic|luxury</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>furn_moonwood_vanity</t>
+        </is>
+      </c>
+      <c r="I193" t="b">
+        <v>1</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="b">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="b">
+        <v>0</v>
+      </c>
+      <c r="S193" t="b">
+        <v>0</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>furn_arcane_hearth</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>秘法壁炉</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E194" t="b">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>furniture|home|stone|magic</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>furn_arcane_hearth</t>
+        </is>
+      </c>
+      <c r="I194" t="b">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="b">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" t="b">
+        <v>0</v>
+      </c>
+      <c r="S194" t="b">
+        <v>0</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -9,7 +9,6 @@
     <sheet name="item" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="item_use" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="item_gift" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="item_tag" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1185,7 +1184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U276"/>
+  <dimension ref="A1:W282"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="26.25" customWidth="1" min="2" max="2"/>
@@ -1305,6 +1304,16 @@
           <t>can_dismantle</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>market_sellable</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>market_base_price</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1412,6 +1421,16 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1519,6 +1538,16 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1624,6 +1653,16 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>是否允许进入分解系统；仍需item_dismantle存在对应规则</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>是否允许进入市集售卖</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>市集基础售价（金币/个）</t>
         </is>
       </c>
     </row>
@@ -20748,6 +20787,480 @@
       </c>
       <c r="U276" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>human_armar_head_lv1</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E277" t="b">
+        <v>0</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>HumanArmar|ArmarHead</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>human_armar_head</t>
+        </is>
+      </c>
+      <c r="J277" t="b">
+        <v>1</v>
+      </c>
+      <c r="K277" t="n">
+        <v>1</v>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" t="b">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="b">
+        <v>0</v>
+      </c>
+      <c r="T277" t="b">
+        <v>0</v>
+      </c>
+      <c r="U277" t="b">
+        <v>0</v>
+      </c>
+      <c r="V277" t="b">
+        <v>1</v>
+      </c>
+      <c r="W277" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>human_armar_chest_lv1</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E278" t="b">
+        <v>0</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>HumanArmar|ArmarChest</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>human_armar_chest</t>
+        </is>
+      </c>
+      <c r="J278" t="b">
+        <v>1</v>
+      </c>
+      <c r="K278" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="b">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="b">
+        <v>0</v>
+      </c>
+      <c r="T278" t="b">
+        <v>0</v>
+      </c>
+      <c r="U278" t="b">
+        <v>0</v>
+      </c>
+      <c r="V278" t="b">
+        <v>1</v>
+      </c>
+      <c r="W278" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>human_armar_hand_lv1</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E279" t="b">
+        <v>0</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>HumanArmar|ArmarHand</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>human_armar_hand</t>
+        </is>
+      </c>
+      <c r="J279" t="b">
+        <v>1</v>
+      </c>
+      <c r="K279" t="n">
+        <v>1</v>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="b">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="b">
+        <v>0</v>
+      </c>
+      <c r="T279" t="b">
+        <v>0</v>
+      </c>
+      <c r="U279" t="b">
+        <v>0</v>
+      </c>
+      <c r="V279" t="b">
+        <v>1</v>
+      </c>
+      <c r="W279" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>human_armar_leg_lv1</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E280" t="b">
+        <v>0</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>HumanArmar|ArmarLeg</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>human_armar_leg</t>
+        </is>
+      </c>
+      <c r="J280" t="b">
+        <v>1</v>
+      </c>
+      <c r="K280" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="b">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="b">
+        <v>0</v>
+      </c>
+      <c r="T280" t="b">
+        <v>0</v>
+      </c>
+      <c r="U280" t="b">
+        <v>0</v>
+      </c>
+      <c r="V280" t="b">
+        <v>1</v>
+      </c>
+      <c r="W280" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>human_armar_foot_lv1</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E281" t="b">
+        <v>0</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>HumanArmar|ArmarFoot</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>human_armar_foot</t>
+        </is>
+      </c>
+      <c r="J281" t="b">
+        <v>1</v>
+      </c>
+      <c r="K281" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="b">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="b">
+        <v>0</v>
+      </c>
+      <c r="T281" t="b">
+        <v>0</v>
+      </c>
+      <c r="U281" t="b">
+        <v>0</v>
+      </c>
+      <c r="V281" t="b">
+        <v>1</v>
+      </c>
+      <c r="W281" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>human_armar_accessory_lv1</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E282" t="b">
+        <v>0</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>HumanArmar|ArmarAccessory</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>human_armar_accessory</t>
+        </is>
+      </c>
+      <c r="J282" t="b">
+        <v>1</v>
+      </c>
+      <c r="K282" t="n">
+        <v>1</v>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="b">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="b">
+        <v>0</v>
+      </c>
+      <c r="T282" t="b">
+        <v>0</v>
+      </c>
+      <c r="U282" t="b">
+        <v>0</v>
+      </c>
+      <c r="V282" t="b">
+        <v>1</v>
+      </c>
+      <c r="W282" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -25126,1169 +25639,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E62"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>hidden</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>requires_instance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EItemTag</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>UI显示字</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>是否在UI标签展示中隐藏</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>是否需要创建实例容器</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Gift</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>礼物提示</t>
-        </is>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PartGear</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>部位装备</t>
-        </is>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>HumanWeapon</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>人类武器</t>
-        </is>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>HumanTool</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>人类工具</t>
-        </is>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Pocket</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>口袋</t>
-        </is>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Insertion</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>插入物</t>
-        </is>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Plant</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>植物</t>
-        </is>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>钥匙</t>
-        </is>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Potion</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>药水</t>
-        </is>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Furniture</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>家具</t>
-        </is>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Dismantleable</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>可分解</t>
-        </is>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Jingyuan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>精元</t>
-        </is>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>小型</t>
-        </is>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Big</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>大型</t>
-        </is>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Material</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>材料</t>
-        </is>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Wood</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>木材</t>
-        </is>
-      </c>
-      <c r="D21" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>魔法</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Alchemy</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>炼金</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Fuel</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>燃料</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Fiber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>纤维</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Stone</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>石材</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Glass</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>玻璃</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Clay</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>黏土</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ceramic</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>陶瓷</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Luxury</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>奢侈品</t>
-        </is>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Craft</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>工艺</t>
-        </is>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Ore</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>矿石</t>
-        </is>
-      </c>
-      <c r="D32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>金属</t>
-        </is>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Precious</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>贵重</t>
-        </is>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Textile</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>纺织</t>
-        </is>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Leather</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>皮革</t>
-        </is>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Bone</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>骨</t>
-        </is>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Dye</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>染料</t>
-        </is>
-      </c>
-      <c r="D38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Glue</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>胶</t>
-        </is>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Latex</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>乳胶</t>
-        </is>
-      </c>
-      <c r="D40" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Exotic</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>异域</t>
-        </is>
-      </c>
-      <c r="D41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Loot</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>杂物</t>
-        </is>
-      </c>
-      <c r="D42" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Paper</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>纸张</t>
-        </is>
-      </c>
-      <c r="D43" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Food</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>食物</t>
-        </is>
-      </c>
-      <c r="D44" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Gel</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>凝胶</t>
-        </is>
-      </c>
-      <c r="D45" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Crystal</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>水晶</t>
-        </is>
-      </c>
-      <c r="D46" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Wax</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>蜡</t>
-        </is>
-      </c>
-      <c r="D47" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Toy</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>玩具</t>
-        </is>
-      </c>
-      <c r="D48" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Decor</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>装饰</t>
-        </is>
-      </c>
-      <c r="D49" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>家园</t>
-        </is>
-      </c>
-      <c r="D50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Study</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>书房</t>
-        </is>
-      </c>
-      <c r="D51" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Church</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>教堂</t>
-        </is>
-      </c>
-      <c r="D52" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>照明</t>
-        </is>
-      </c>
-      <c r="D53" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Forest</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>森林</t>
-        </is>
-      </c>
-      <c r="D54" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Storage</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>仓储</t>
-        </is>
-      </c>
-      <c r="D55" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>设施</t>
-        </is>
-      </c>
-      <c r="D56" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>基础</t>
-        </is>
-      </c>
-      <c r="D57" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Salvage</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>回收</t>
-        </is>
-      </c>
-      <c r="D58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Dew</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>露水</t>
-        </is>
-      </c>
-      <c r="D59" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Fairy</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>妖精</t>
-        </is>
-      </c>
-      <c r="D60" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>充能</t>
-        </is>
-      </c>
-      <c r="D61" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="n">
-        <v>58</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Premium Essence Drop</t>
-        </is>
-      </c>
-      <c r="D62" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Config/Datas/item.xlsx
+++ b/Config/Datas/item.xlsx
@@ -2,16 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="item_use" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="item_gift" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -21,160 +17,117 @@
   <fonts count="21">
     <font>
       <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="18"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <i val="1"/>
       <color rgb="FF7F7F7F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="15"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="13"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="134"/>
       <b val="1"/>
       <color theme="3"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FF3F3F76"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FFFA7D00"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color theme="0"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -187,198 +140,161 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.79998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.59999"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="9">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
@@ -392,25 +308,16 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -425,7 +332,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -440,7 +346,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -455,44 +360,36 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
@@ -501,7 +398,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
@@ -629,70 +526,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
@@ -725,8 +620,7 @@
         <color theme="0"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
+        <patternFill>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
@@ -748,21 +642,17 @@
         <bottom style="thin">
           <color theme="4"/>
         </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
@@ -771,14 +661,13 @@
         <b val="1"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
@@ -793,7 +682,7 @@
       </font>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
@@ -819,17 +708,15 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
     </dxf>
@@ -839,17 +726,16 @@
         <color theme="1"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </top>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
@@ -859,41 +745,17 @@
         <color theme="1"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998"/>
         </patternFill>
       </fill>
       <border>
         <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39998"/>
         </bottom>
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1174,7 +1036,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
@@ -1184,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W282"/>
+  <dimension ref="A1:W291"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="26.25" customWidth="1" min="2" max="2"/>
@@ -21263,6 +21124,687 @@
         <v>100</v>
       </c>
     </row>
+    <row r="283">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>herb_poultice</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>草药敷剂</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E283" t="b">
+        <v>1</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Tiny</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Potion</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>berry</t>
+        </is>
+      </c>
+      <c r="J283" t="b">
+        <v>1</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="b">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="b">
+        <v>0</v>
+      </c>
+      <c r="T283" t="b">
+        <v>0</v>
+      </c>
+      <c r="U283" t="b">
+        <v>0</v>
+      </c>
+      <c r="V283" t="b">
+        <v>0</v>
+      </c>
+      <c r="W283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>furn_basic_cauldron</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>陶土炼金釜</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E284" t="b">
+        <v>0</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>5|19|52</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>mat_charcoal</t>
+        </is>
+      </c>
+      <c r="J284" t="b">
+        <v>1</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v>0</v>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="b">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="b">
+        <v>0</v>
+      </c>
+      <c r="T284" t="b">
+        <v>0</v>
+      </c>
+      <c r="U284" t="b">
+        <v>0</v>
+      </c>
+      <c r="V284" t="b">
+        <v>0</v>
+      </c>
+      <c r="W284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>furn_stone_retort</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>石制蒸馏釜</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E285" t="b">
+        <v>0</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>5|19|52</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>mat_charcoal</t>
+        </is>
+      </c>
+      <c r="J285" t="b">
+        <v>1</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="b">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="b">
+        <v>0</v>
+      </c>
+      <c r="T285" t="b">
+        <v>0</v>
+      </c>
+      <c r="U285" t="b">
+        <v>0</v>
+      </c>
+      <c r="V285" t="b">
+        <v>0</v>
+      </c>
+      <c r="W285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>furn_arcane_crucible</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>秘仪坩埚</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E286" t="b">
+        <v>0</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>5|19|52</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>mat_charcoal</t>
+        </is>
+      </c>
+      <c r="J286" t="b">
+        <v>1</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="b">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0</v>
+      </c>
+      <c r="S286" t="b">
+        <v>0</v>
+      </c>
+      <c r="T286" t="b">
+        <v>0</v>
+      </c>
+      <c r="U286" t="b">
+        <v>0</v>
+      </c>
+      <c r="V286" t="b">
+        <v>0</v>
+      </c>
+      <c r="W286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>tool_mortar</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>研钵</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E287" t="b">
+        <v>0</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>5|19|27</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>chanzi</t>
+        </is>
+      </c>
+      <c r="J287" t="b">
+        <v>1</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="b">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="b">
+        <v>0</v>
+      </c>
+      <c r="T287" t="b">
+        <v>0</v>
+      </c>
+      <c r="U287" t="b">
+        <v>0</v>
+      </c>
+      <c r="V287" t="b">
+        <v>0</v>
+      </c>
+      <c r="W287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>tool_glass_rod</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>玻璃搅拌棒</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E288" t="b">
+        <v>0</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>5|19|23</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>chanzi</t>
+        </is>
+      </c>
+      <c r="J288" t="b">
+        <v>1</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="b">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="b">
+        <v>0</v>
+      </c>
+      <c r="T288" t="b">
+        <v>0</v>
+      </c>
+      <c r="U288" t="b">
+        <v>0</v>
+      </c>
+      <c r="V288" t="b">
+        <v>0</v>
+      </c>
+      <c r="W288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>tool_alchemy_kit</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>炼金工具包</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E289" t="b">
+        <v>0</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>5|19|27</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>chanzi</t>
+        </is>
+      </c>
+      <c r="J289" t="b">
+        <v>1</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="b">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="b">
+        <v>0</v>
+      </c>
+      <c r="T289" t="b">
+        <v>0</v>
+      </c>
+      <c r="U289" t="b">
+        <v>0</v>
+      </c>
+      <c r="V289" t="b">
+        <v>0</v>
+      </c>
+      <c r="W289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>flash_grenade</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>闪光弹</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E290" t="b">
+        <v>1</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>8</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>smoke_grenade</t>
+        </is>
+      </c>
+      <c r="J290" t="b">
+        <v>1</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S290" t="b">
+        <v>0</v>
+      </c>
+      <c r="T290" t="b">
+        <v>0</v>
+      </c>
+      <c r="U290" t="b">
+        <v>0</v>
+      </c>
+      <c r="V290" t="b">
+        <v>0</v>
+      </c>
+      <c r="W290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>caltrop_bundle</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>铁蒺藜</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="E291" t="b">
+        <v>1</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>8</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>small_stone</t>
+        </is>
+      </c>
+      <c r="J291" t="b">
+        <v>1</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S291" t="b">
+        <v>0</v>
+      </c>
+      <c r="T291" t="b">
+        <v>0</v>
+      </c>
+      <c r="U291" t="b">
+        <v>0</v>
+      </c>
+      <c r="V291" t="b">
+        <v>0</v>
+      </c>
+      <c r="W291" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21274,7 +21816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="21.75" customWidth="1" min="3" max="3"/>
@@ -21726,6 +22268,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" t="n">
         <v>4</v>
@@ -21901,13 +22444,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>item_throw_smoke_grenade</t>
+          <t>item_throw_sound_ball</t>
         </is>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" t="n">
         <v>11</v>
@@ -25463,6 +26007,74 @@
       </c>
       <c r="O92" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>flash_grenade</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>StackCount</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>UseSkill</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>item_throw_flash_grenade</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="n">
+        <v>9</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>caltrop_bundle</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>StackCount</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>UseSkill</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>item_throw_caltrop</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -25477,7 +26089,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
